--- a/Result/checksun_type/零售.xlsx
+++ b/Result/checksun_type/零售.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>213.6</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>215</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>219.86</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>219.86</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>214.05</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>215.32</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>220.44</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>215.32</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>220.44</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>214.35</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>215.5</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>221.05</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>221.05</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,7 +4641,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>214.75</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>215.7</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>221.67</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>215.7</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>221.67</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,7 +5627,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>215.2</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>216.02</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>222.29</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>216.02</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>222.29</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,7 +6613,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>215.8</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>216.42</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>222.95</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>216.42</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>222.95</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,7 +7599,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
@@ -7590,7 +7614,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>216.25</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>216.92</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>223.58</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>216.92</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>223.58</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,7 +8585,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
@@ -8572,7 +8600,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>216.55</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>217.42</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>224.14</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>217.42</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>224.14</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,7 +9571,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
@@ -9554,7 +9586,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>216.55</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>217.85</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>224.63</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>217.85</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>224.63</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>

--- a/Result/checksun_type/零售.xlsx
+++ b/Result/checksun_type/零售.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2981.945</t>
+          <t>1150.568</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.10931235303462698</t>
+          <t>-0.0015658716132489568</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.725</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>219.4009568337635</t>
+          <t>219.4095209832132</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>210.5990431662365</t>
+          <t>210.0404790167868</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.04093913333733463</t>
+          <t>0.04363274870847074</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.001509346336932449</t>
+          <t>-0.001279069767441854</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0006322047883784432</t>
+          <t>3.903423926954197e-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.1194388933028725</t>
+          <t>0.065795612938224</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.09643558606313925</t>
+          <t>0.07499018369124305</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.8440885667630521</t>
+          <t>0.9130721947444821</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-1004417.0</t>
+          <t>-298081.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>241000.0</t>
+          <t>172000.0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1020000.0</t>
+          <t>1032000.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-779000.0</t>
+          <t>-860000.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>62058.0</t>
+          <t>48058.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-1721359.0</t>
+          <t>-1110023.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,307 +1849,307 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>-0.71</v>
+        <v>-0.33</v>
       </c>
       <c r="CL2" t="n">
-        <v>-1.4</v>
+        <v>-1.41</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
+          <t>211.7</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>212.95</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>214.72</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>219.34</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>224.42</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>226.1395833333333</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>-0.001415094339622724</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>-0.003043071161048738</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>-0.001279069767441854</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>-0.002365141453652408</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>-0.0007235688642752702</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>-0.0006536669796902705</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>-6.95</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>-153.39</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>401567743.4</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>402197533.1</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>360892111.8</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>499527332.66</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>636367710.4625</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>-2799714.512700467</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>11251584.0961445</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>-6.64</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>19.01</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>79.08</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>219360</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>213.6</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>215.0</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>219.86</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>224.58</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>-0.002352941176470558</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>-0.002102312543798224</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>-0.001509346336932449</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>-0.002631101433496541</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>-0.0006396707086437914</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>-7.43</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>-152.47</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>446456989.4</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>402462830.4</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>367213800.2333333</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>514612178.2</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>644200383.275</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>-5354496.075872992</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>28645776.31716985</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>-6.86</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>80.68</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>218840</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ER2" t="inlineStr">
         <is>
           <t>210.0</t>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2207.66</t>
+          <t>2981.945</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,359 +2444,359 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>210.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.10931235303462698</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>219.4009568337682</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>210.5990431662318</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.04093913333737826</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.0006322047883757786</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.1194388933025705</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.07499018369124305</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.8440885667632837</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>-298081.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>172000.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>1032000.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-860000.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>48058.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-1110023.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.1244041204927823</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>215.325</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>219.2623381336843</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>211.3876618663157</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.0365711193190232</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0002231618605752494</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.06116199241285347</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.09643558606313925</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.7416038667762083</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-1004417.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>241000.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>1020000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-779000.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>62058.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-1721359.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,17 +2835,17 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -2854,283 +2854,283 @@
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="CL3" t="n">
-        <v>-1.31</v>
+        <v>-1.4</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>213.6</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>219.86</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>224.58</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>226.2875</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>-0.002352941176470558</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>-0.002102312543798224</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>-0.002631101433496541</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>-0.0006396707086437914</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>-0.0006900168364107895</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>-7.43</t>
+        </is>
+      </c>
+      <c r="DB3" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>-152.47</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DI3" t="n">
+        <v>446456989.4</v>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>402462830.4</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>367213800.2333333</t>
+        </is>
+      </c>
+      <c r="DL3" t="n">
+        <v>514612178.2</v>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>644200383.275</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>-5354496.077945007</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>28645776.31672496</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>-6.86</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>19.01</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>79.08</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>219360</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>214.05</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>215.32</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>220.44</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>224.72</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>-0.00140977443609025</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>-0.001399580125962085</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>-0.00275955666138894</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>-0.001083483817196806</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>-3.62</t>
-        </is>
-      </c>
-      <c r="DB3" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>-151.49</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DI3" t="n">
-        <v>418130651</v>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>371868657.7</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>365219125.0</t>
-        </is>
-      </c>
-      <c r="DL3" t="n">
-        <v>527411299.66</v>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>653166606.5875</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>-11536363.78369896</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>11185010.22817957</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR3" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS3" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT3" t="inlineStr">
-        <is>
-          <t>-5.97</t>
-        </is>
-      </c>
-      <c r="DU3" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV3" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW3" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ3" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>5.39</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK3" t="inlineStr">
-        <is>
-          <t>80.68</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr">
-        <is>
-          <t>218840</t>
-        </is>
-      </c>
-      <c r="EM3" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN3" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO3" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP3" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
       <c r="EQ3" t="inlineStr">
         <is>
           <t>212.5</t>
@@ -3138,14 +3138,14 @@
       </c>
       <c r="ER3" t="inlineStr">
         <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ES3" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET3" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1661.585</t>
+          <t>2207.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.04757601939330377</t>
+          <t>0.1244041204927823</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.325</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>219.2134180594471</t>
+          <t>219.2623381336896</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>211.7865819405529</t>
+          <t>211.3876618663104</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.03446327665380133</t>
+          <t>0.03657111931907204</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0009272137227630539</t>
+          <t>-0.0008120649651972567</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0002666812745708569</t>
+          <t>0.0002231618605739172</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.07580111770079268</t>
+          <t>0.06116199241267872</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.09643558606313925</t>
+          <t>0.07499018369124305</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6844365996146634</t>
+          <t>0.7416038667766317</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>弱勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -3690,32 +3690,32 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-1004417.0</t>
+          <t>-298081.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>241000.0</t>
+          <t>172000.0</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1020000.0</t>
+          <t>1032000.0</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-779000.0</t>
+          <t>-860000.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>62058.0</t>
+          <t>48058.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-1721359.0</t>
+          <t>-1110023.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,12 +3821,12 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -3836,162 +3836,162 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>-1.25</v>
+        <v>-1.31</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>212.8</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>214.35</t>
+          <t>214.05</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.32</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>221.05</t>
+          <t>220.44</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>224.97</t>
+          <t>224.72</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
+          <t>226.44375</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>-0.00140977443609025</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>-0.001399580125962085</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>-0.0008120649651972567</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>-0.00275955666138894</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>-0.001083483817196806</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>-0.0006527895259461625</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>-3.62</t>
+        </is>
+      </c>
+      <c r="DB4" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>-151.49</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>467278976.0</t>
+        </is>
+      </c>
+      <c r="DI4" t="n">
+        <v>418130651</v>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>371868657.7</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>365219125.0</t>
+        </is>
+      </c>
+      <c r="DL4" t="n">
+        <v>527411299.66</v>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>653166606.5875</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>-11536363.78606682</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>11185010.22767115</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>467278976.0</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>-0.002344116268166885</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>-0.001862630966239842</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>-0.0009272137227630539</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>-0.002796950421798061</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>-0.00185791137485436</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>-5.27</t>
-        </is>
-      </c>
-      <c r="DB4" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>-151.02</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>353129823.0</t>
-        </is>
-      </c>
-      <c r="DI4" t="n">
-        <v>366032679.6</v>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>349409181.6</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>361747717.0333334</t>
-        </is>
-      </c>
-      <c r="DL4" t="n">
-        <v>541988911.52</v>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>663738938.0125</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>-15667522.6949496</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>3061425.80718708</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>353129823.0</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
@@ -4114,17 +4114,17 @@
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ER4" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="ES4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1493.082</t>
+          <t>1661.585</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.02818205226401916</t>
+          <t>0.04757601939330377</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>219.1549735317771</t>
+          <t>219.2134180594527</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>212.2450264682229</t>
+          <t>211.7865819405473</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.03203498870447023</t>
+          <t>0.03446327665385303</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0015044555028354</t>
+          <t>-0.0009272137227630539</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0003340450614949253</t>
+          <t>0.0002666812745690805</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.08022388064298025</t>
+          <t>0.07580111770054776</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.09643558606313925</t>
+          <t>0.07499018369124305</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.622715206731353</t>
+          <t>0.6844365996151905</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>False</t>
@@ -4661,14 +4661,14 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
           <t>弱勢</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="BE5" t="inlineStr">
         <is>
           <t>83.3</t>
@@ -4676,32 +4676,32 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-1004417.0</t>
+          <t>-298081.0</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>241000.0</t>
+          <t>172000.0</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1020000.0</t>
+          <t>1032000.0</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-779000.0</t>
+          <t>-860000.0</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>62058.0</t>
+          <t>48058.0</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-1721359.0</t>
+          <t>-1110023.0</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,177 +4807,177 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>-0.61</v>
+        <v>-0.14</v>
       </c>
       <c r="CL5" t="n">
-        <v>-1.11</v>
+        <v>-1.25</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>213.3</t>
+          <t>212.8</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>214.75</t>
+          <t>214.35</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>221.67</t>
+          <t>221.05</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>225.39</t>
+          <t>224.97</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
+          <t>226.5916666666667</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>-0.002344116268166885</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>-0.001862630966239842</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>-0.0009272137227630539</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>-0.002796950421798061</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>-0.00185791137485436</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>-0.000652363669775391</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>-5.27</t>
+        </is>
+      </c>
+      <c r="DB5" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>-151.02</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>353129823.0</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>366032679.6</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>349409181.6</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>361747717.0333334</t>
+        </is>
+      </c>
+      <c r="DL5" t="n">
+        <v>541988911.52</v>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>663738938.0125</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>-15667522.69765554</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>3061425.806606054</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>353129823.0</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>-0.004201680672268782</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>-0.002091078066914442</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>-0.0015044555028354</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>-0.002789149309460615</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>-0.001495182190718869</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>-6.02</t>
-        </is>
-      </c>
-      <c r="DB5" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>-150.35</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH5" t="inlineStr">
-        <is>
-          <t>316776227.0</t>
-        </is>
-      </c>
-      <c r="DI5" t="n">
-        <v>345663307.4</v>
-      </c>
-      <c r="DJ5" t="inlineStr">
-        <is>
-          <t>336188816.6</t>
-        </is>
-      </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>367617217.2</t>
-        </is>
-      </c>
-      <c r="DL5" t="n">
-        <v>561834701.02</v>
-      </c>
-      <c r="DM5" t="inlineStr">
-        <is>
-          <t>700692145.4125</t>
-        </is>
-      </c>
-      <c r="DN5" t="inlineStr">
-        <is>
-          <t>-19072786.05897446</t>
-        </is>
-      </c>
-      <c r="DO5" t="inlineStr">
-        <is>
-          <t>3577234.962655425</t>
-        </is>
-      </c>
-      <c r="DP5" t="inlineStr">
-        <is>
-          <t>316776227.0</t>
-        </is>
-      </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
@@ -5035,22 +5035,22 @@
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5100,22 +5100,22 @@
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2196.33</t>
+          <t>1493.082</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,359 +5402,359 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.02818205226401916</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>215.7</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>219.1549735317831</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>212.2450264682169</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.03203498870452557</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.0015044555028354</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.0003340450614971457</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.08022388064267094</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.07499018369124305</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.6227152067319971</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>-298081.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>172000.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>1032000.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-860000.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>48058.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>-1110023.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.22693734286617706</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>216.025</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>219.2282056312086</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>212.8217943687914</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.02965587900667599</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.001848215317084456</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.002463797900748133</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.04052320117718478</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.09643558606313925</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.5639431230726679</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-1004417.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>241000.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>1020000.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-779000.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>62058.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>-1721359.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,12 +5793,12 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -5812,158 +5812,158 @@
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-0.79</v>
+        <v>-0.61</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.84</v>
+        <v>-1.11</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>214.2</t>
+          <t>213.3</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>215.2</t>
+          <t>214.75</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>216.02</t>
+          <t>215.7</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>222.29</t>
+          <t>221.67</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>225.39</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>226.7395833333333</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>-0.004201680672268782</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>-0.002091078066914442</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>-0.0015044555028354</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>-0.002789149309460615</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>-0.001495182190718869</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>-0.000661114528909934</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>-6.02</t>
+        </is>
+      </c>
+      <c r="DB6" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>-150.35</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>316776227.0</t>
+        </is>
+      </c>
+      <c r="DI6" t="n">
+        <v>345663307.4</v>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>336188816.6</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>367617217.2</t>
+        </is>
+      </c>
+      <c r="DL6" t="n">
+        <v>561834701.02</v>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>700692145.4125</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>-19072786.06206674</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>3577234.96199137</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>316776227.0</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>-0.004646840148698872</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>-0.002780352177942591</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>-0.001848215317084456</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>-0.002960305001121322</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>-0.001133943634704204</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>-2.73</t>
-        </is>
-      </c>
-      <c r="DB6" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>-149.59</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>467102515.0</t>
-        </is>
-      </c>
-      <c r="DI6" t="n">
-        <v>402827322.8</v>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>328319392.3</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>376703314.4666666</t>
-        </is>
-      </c>
-      <c r="DL6" t="n">
-        <v>582922481.98</v>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>734035263.775</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>-23190971.6992708</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>8081374.936086774</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>467102515.0</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6091,19 +6091,19 @@
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ES6" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET6" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6363,7 +6363,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2277.177</t>
+          <t>2196.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.15575456569198345</t>
+          <t>0.22693734286617706</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -6468,47 +6468,47 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>216.425</t>
+          <t>216.025</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>219.7696736918988</t>
+          <t>219.228205631215</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>213.0803263081012</t>
+          <t>212.821794368785</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.03090838574008341</t>
+          <t>0.02965587900673572</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0023049441051054</t>
+          <t>-0.001848215317084456</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.005655295743214994</t>
+          <t>-0.002463797900746689</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.1812639188512785</t>
+          <t>-0.04052320117702157</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.09643558606313925</t>
+          <t>0.07499018369124305</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.5727216399701731</t>
+          <t>0.563943123073434</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -6568,127 +6568,127 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>-298081.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>172000.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>1032000.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-860000.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>48058.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-1110023.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-1004417.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>241000.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1020000.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-779000.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>62058.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>-1721359.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,12 +6779,12 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -6798,158 +6798,158 @@
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-1.02</v>
+        <v>-0.79</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.57</v>
+        <v>-0.84</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
+          <t>214.2</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
           <t>215.2</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
-        <is>
-          <t>215.8</t>
-        </is>
-      </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>216.42</t>
+          <t>216.02</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>222.95</t>
+          <t>222.29</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>225.98</t>
+          <t>225.72</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>226.8895833333333</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>-0.004646840148698872</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>-0.002780352177942591</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>-0.001848215317084456</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>-0.002960305001121322</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>-0.001133943634704204</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>-0.0006973564684401579</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>-2.73</t>
+        </is>
+      </c>
+      <c r="DB7" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>-149.59</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>467102515.0</t>
+        </is>
+      </c>
+      <c r="DI7" t="n">
+        <v>402827322.8</v>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>328319392.3</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>376703314.4666666</t>
+        </is>
+      </c>
+      <c r="DL7" t="n">
+        <v>582922481.98</v>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>734035263.775</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>-23190971.70280458</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>8081374.935327888</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>467102515.0</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
-        <is>
-          <t>-0.001855287569573316</t>
-        </is>
-      </c>
-      <c r="CV7" t="inlineStr">
-        <is>
-          <t>-0.002080924855491273</t>
-        </is>
-      </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>-0.0023049441051054</t>
-        </is>
-      </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>-0.002817783343769698</t>
-        </is>
-      </c>
-      <c r="CY7" t="inlineStr">
-        <is>
-          <t>-0.0008014149118443781</t>
-        </is>
-      </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA7" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="DB7" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="DD7" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>-149.26</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>486365714.0</t>
-        </is>
-      </c>
-      <c r="DI7" t="n">
-        <v>358468671.4</v>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>310159857.5</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>389696834.5333334</t>
-        </is>
-      </c>
-      <c r="DL7" t="n">
-        <v>598546724.48</v>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>767533169.1875</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>-28876852.90569945</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>-1879147.921014369</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>486365714.0</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR7" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,22 +7007,22 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7072,22 +7072,22 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>963.738</t>
+          <t>2277.177</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.13009957206955292</t>
+          <t>0.15575456569198345</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7454,47 +7454,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>216.925</t>
+          <t>216.425</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>221.0196049227857</t>
+          <t>219.769673691905</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>212.8303950772143</t>
+          <t>213.0803263080951</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.0377513419180423</t>
+          <t>0.03090838574014041</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.00229964355524892</t>
+          <t>-0.0023049441051054</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.006071372308859679</t>
+          <t>-0.005655295743209665</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.1700107926476495</t>
+          <t>-0.1812639188507745</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.09643558606313925</t>
+          <t>0.07499018369124305</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.6749265067734521</t>
+          <t>0.5727216399708794</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -7549,14 +7549,14 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AQ8" t="inlineStr">
         <is>
           <t>False</t>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7634,32 +7634,32 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-1004417.0</t>
+          <t>-298081.0</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>241000.0</t>
+          <t>172000.0</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1020000.0</t>
+          <t>1032000.0</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-779000.0</t>
+          <t>-860000.0</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>62058.0</t>
+          <t>48058.0</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-1721359.0</t>
+          <t>-1110023.0</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,12 +7765,12 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -7780,162 +7780,162 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-0.74</v>
+        <v>-1.02</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>215.6</t>
+          <t>215.2</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>216.25</t>
+          <t>215.8</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>216.92</t>
+          <t>216.42</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>223.58</t>
+          <t>222.95</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>226.16</t>
+          <t>225.98</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>227.0479166666667</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>-0.001855287569573316</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>-0.002080924855491273</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>-0.0023049441051054</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>-0.002817783343769698</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>-0.0008014149118443781</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>-0.0006418897233454457</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DB8" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>-149.26</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>486365714.0</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>358468671.4</v>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>310159857.5</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>389696834.5333334</t>
+        </is>
+      </c>
+      <c r="DL8" t="n">
+        <v>598546724.48</v>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>767533169.1875</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>-28876852.90973775</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>-1879147.921881616</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>486365714.0</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>-0.001389532190829157</t>
-        </is>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>-0.001385361348418379</t>
-        </is>
-      </c>
-      <c r="CW8" t="inlineStr">
-        <is>
-          <t>-0.00229964355524892</t>
-        </is>
-      </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>-0.002498438475952436</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>7.96</t>
-        </is>
-      </c>
-      <c r="DB8" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="DD8" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE8" t="inlineStr">
-        <is>
-          <t>-149.49</t>
-        </is>
-      </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG8" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH8" t="inlineStr">
-        <is>
-          <t>206789119.0</t>
-        </is>
-      </c>
-      <c r="DI8" t="n">
-        <v>325606664.4</v>
-      </c>
-      <c r="DJ8" t="inlineStr">
-        <is>
-          <t>288122102.2</t>
-        </is>
-      </c>
-      <c r="DK8" t="inlineStr">
-        <is>
-          <t>382161641.2333333</t>
-        </is>
-      </c>
-      <c r="DL8" t="n">
-        <v>606980317.38</v>
-      </c>
-      <c r="DM8" t="inlineStr">
-        <is>
-          <t>803541390.0625</t>
-        </is>
-      </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>-33785526.53927855</t>
-        </is>
-      </c>
-      <c r="DO8" t="inlineStr">
-        <is>
-          <t>-18105268.04112267</t>
-        </is>
-      </c>
-      <c r="DP8" t="inlineStr">
-        <is>
-          <t>206789119.0</t>
-        </is>
-      </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8058,22 +8058,22 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
@@ -8098,42 +8098,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8143,22 +8143,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1167.249</t>
+          <t>963.738</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.07424163374669263</t>
+          <t>0.13009957206955292</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -8440,47 +8440,47 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>217.425</t>
+          <t>216.925</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>222.3696941260321</t>
+          <t>221.0196049227907</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>212.4803058739679</t>
+          <t>212.8303950772093</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.04548413591842761</t>
+          <t>0.03775134191808868</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.001950883635528977</t>
+          <t>-0.00229964355524892</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.004377368199253939</t>
+          <t>-0.006071372308855794</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.09877605190323402</t>
+          <t>-0.1700107926473311</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.09643558606313925</t>
+          <t>0.07499018369124305</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.7647884366920481</t>
+          <t>0.6749265067739033</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -8525,24 +8525,24 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>False</t>
@@ -8620,32 +8620,32 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-1004417.0</t>
+          <t>-298081.0</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>241000.0</t>
+          <t>172000.0</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1020000.0</t>
+          <t>1032000.0</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-779000.0</t>
+          <t>-860000.0</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>62058.0</t>
+          <t>48058.0</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-1721359.0</t>
+          <t>-1110023.0</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,12 +8751,12 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -8766,43 +8766,43 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-0.42</v>
+        <v>-0.74</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.7</v>
+        <v>-0.61</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>215.9</t>
+          <t>215.6</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>216.25</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>217.42</t>
+          <t>216.92</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>224.14</t>
+          <t>223.58</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -8812,116 +8812,116 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
+          <t>227.19375</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>-0.001389532190829157</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>-0.001385361348418379</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>-0.00229964355524892</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>-0.002498438475952436</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>-0.0006597938144330406</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>7.96</t>
+        </is>
+      </c>
+      <c r="DB9" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>-149.49</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>206789119.0</t>
+        </is>
+      </c>
+      <c r="DI9" t="n">
+        <v>325606664.4</v>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>288122102.2</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>382161641.2333333</t>
+        </is>
+      </c>
+      <c r="DL9" t="n">
+        <v>606980317.38</v>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>803541390.0625</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>-33785526.54389341</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>-18105268.04211378</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>206789119.0</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>-0.001387604070305248</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>-0.001950883635528977</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>-0.002181364911187367</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>0.0004423555432677695</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>13.21</t>
-        </is>
-      </c>
-      <c r="DB9" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>-150.47</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>251282962.0</t>
-        </is>
-      </c>
-      <c r="DI9" t="n">
-        <v>332785683.6</v>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>309786618.9</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>398030621.5</t>
-        </is>
-      </c>
-      <c r="DL9" t="n">
-        <v>615894844.5599999</v>
-      </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>847038492.3375</t>
-        </is>
-      </c>
-      <c r="DN9" t="inlineStr">
-        <is>
-          <t>-36636482.62985235</t>
-        </is>
-      </c>
-      <c r="DO9" t="inlineStr">
-        <is>
-          <t>-10684187.74695152</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>251282962.0</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9054,12 +9054,12 @@
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
@@ -9084,42 +9084,42 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2787.692</t>
+          <t>1167.249</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.04309747478914503</t>
+          <t>0.07424163374669263</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>217.85</t>
+          <t>217.425</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>223.3473677911883</t>
+          <t>222.3696941260363</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>212.3526322088117</t>
+          <t>212.4803058739638</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.05046929346971137</t>
+          <t>0.04548413591846603</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.001604032997250204</t>
+          <t>-0.001950883635528977</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.003818584124711033</t>
+          <t>-0.004377368199252052</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.08283621009937248</t>
+          <t>-0.09877605190308758</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.09643558606313925</t>
+          <t>0.07499018369124305</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.7947514708842507</t>
+          <t>0.7647884366923113</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9511,24 +9511,24 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>False</t>
@@ -9606,32 +9606,32 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-1004417.0</t>
+          <t>-298081.0</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>241000.0</t>
+          <t>172000.0</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1020000.0</t>
+          <t>1032000.0</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-779000.0</t>
+          <t>-860000.0</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>62058.0</t>
+          <t>48058.0</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-1721359.0</t>
+          <t>-1110023.0</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,17 +9737,17 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>57</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -9756,24 +9756,24 @@
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>0.14</v>
+        <v>-0.42</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0.76</v>
+        <v>-0.7</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>216.2</t>
+          <t>215.9</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -9783,131 +9783,131 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>217.85</t>
+          <t>217.42</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>224.63</t>
+          <t>224.14</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>226.06</t>
+          <t>226.16</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>227.34375</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>-0.001387604070305248</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>-0.001950883635528977</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>-0.002181364911187367</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>0.0004423555432677695</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>-0.0006410549933605347</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>13.21</t>
+        </is>
+      </c>
+      <c r="DB10" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>-150.47</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>871548215.6657143</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>251282962.0</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>332785683.6</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>309786618.9</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>398030621.5</t>
+        </is>
+      </c>
+      <c r="DL10" t="n">
+        <v>615894844.5599999</v>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>847038492.3375</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>-36636482.63512607</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>-10684187.74808425</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>251282962.0</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>0.0002309468822172533</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>-0.001604032997250204</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>-0.002176616915422924</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>0.0005532503457814641</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>16.70</t>
-        </is>
-      </c>
-      <c r="DB10" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>-152.14</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>1120433522.231527</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>602596304.0</t>
-        </is>
-      </c>
-      <c r="DI10" t="n">
-        <v>326714325.8</v>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>313215527.5</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>400782221.6666667</t>
-        </is>
-      </c>
-      <c r="DL10" t="n">
-        <v>622182992.9</v>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>884087304.15</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>-41355081.69947068</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>-4468263.800030172</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>602596304.0</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>219360</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>217.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>217.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
@@ -10070,42 +10070,42 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/零售.xlsx
+++ b/Result/checksun_type/零售.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1150.568</t>
+          <t>1565.939</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0015658716132489568</t>
+          <t>0.07804088643049134</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>214.725</t>
+          <t>214.45</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>219.4095209832132</t>
+          <t>219.4542087549558</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>210.0404790167868</t>
+          <t>209.4457912450442</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.04363274870847074</t>
+          <t>0.04667016791751722</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.001279069767441854</t>
+          <t>-0.001280707882174936</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.903423926954197e-05</t>
+          <t>0.0002036728923464626</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.065795612938224</t>
+          <t>0.0696132904526523</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.07499018369124305</t>
+          <t>0.0958841438292665</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.9130721947444821</t>
+          <t>0.988611689761863</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,142 +1623,142 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>307351.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>184000.0</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>1017000.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>-833000.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>-506591.0</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-298081.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>172000.0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>1032000.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>-860000.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>48058.0</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>-1110023.0</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,110 +1849,110 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>-1.41</v>
+        <v>-1.42</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>211.7</t>
+          <t>211.4</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>212.95</t>
+          <t>212.35</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>214.45</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>219.34</t>
+          <t>218.73</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>224.42</t>
+          <t>224.21</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>226.1395833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>-0.001415094339622724</t>
+          <t>-0.001417099669343336</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>-0.003043071161048738</t>
+          <t>-0.002817562808170915</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>-0.001279069767441854</t>
+          <t>-0.001280707882174936</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>-0.002365141453652408</t>
+          <t>-0.002781070484179859</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>-0.0007235688642752702</t>
+          <t>-0.0009468905784386639</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>-0.0006536669796902705</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.80</t>
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>-2.34</v>
+        <v>-2.38</v>
       </c>
       <c r="DC2" t="n">
-        <v>-2.19</v>
+        <v>-2.23</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-153.39</t>
+          <t>-154.32</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1971,48 +1971,48 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>871548215.6657143</t>
+          <t>1113691511.663414</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>242656285.0</t>
+          <t>329846967.0</t>
         </is>
       </c>
       <c r="DI2" t="n">
-        <v>401567743.4</v>
+        <v>404181891.4</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>402197533.1</t>
+          <t>374922599.4</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>360892111.8</t>
+          <t>330701942.7</t>
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>499527332.66</v>
+        <v>492655844.94</v>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>636367710.4625</t>
+          <t>630795391.725</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-2799714.512700467</t>
+          <t>-1548425.956954639</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>11251584.0961445</t>
+          <t>5333661.089675188</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>242656285.0</t>
+          <t>329846967.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>218840</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2981.945</t>
+          <t>1150.568</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.10931235303462698</t>
+          <t>-0.0015658716132489568</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.725</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>219.4009568337682</t>
+          <t>219.4095209832088</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>210.5990431662318</t>
+          <t>210.0404790167912</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.04093913333737826</t>
+          <t>0.04363274870842971</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.001509346336932449</t>
+          <t>-0.001279069767441854</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0006322047883757786</t>
+          <t>3.903423927087424e-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.1194388933025705</t>
+          <t>0.06579561293835745</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.07499018369124305</t>
+          <t>0.0958841438292665</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.8440885667632837</t>
+          <t>0.9130721947443678</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2609,142 +2609,142 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>307351.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>184000.0</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>1017000.0</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>-833000.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>-506591.0</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-298081.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>172000.0</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>1032000.0</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>-860000.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>48058.0</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>-1110023.0</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,307 +2835,307 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>-0.71</v>
+        <v>-0.33</v>
       </c>
       <c r="CL3" t="n">
-        <v>-1.4</v>
+        <v>-1.41</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
+          <t>211.7</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>212.95</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>214.72</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>219.34</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>224.42</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>-0.001415094339622724</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>-0.003043071161048738</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>-0.001279069767441854</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>-0.002365141453652408</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>-0.0007235688642752702</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>-6.95</t>
+        </is>
+      </c>
+      <c r="DB3" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>-153.39</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>1113691511.663414</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DI3" t="n">
+        <v>401567743.4</v>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>402197533.1</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>360892111.8</t>
+        </is>
+      </c>
+      <c r="DL3" t="n">
+        <v>499527332.66</v>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>636367710.4625</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>-2799714.510887335</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>11251584.09653378</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>-6.64</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>79.04</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>218840</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>213.6</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>215.0</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>219.86</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>224.58</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>226.2875</t>
-        </is>
-      </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>-0.002352941176470558</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>-0.002102312543798224</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>-0.001509346336932449</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>-0.002631101433496541</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>-0.0006396707086437914</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>-0.0006900168364107895</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>-7.43</t>
-        </is>
-      </c>
-      <c r="DB3" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>-152.47</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>871548215.6657143</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DI3" t="n">
-        <v>446456989.4</v>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>402462830.4</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>367213800.2333333</t>
-        </is>
-      </c>
-      <c r="DL3" t="n">
-        <v>514612178.2</v>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>644200383.275</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>-5354496.077945007</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>28645776.31672496</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR3" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS3" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT3" t="inlineStr">
-        <is>
-          <t>-6.86</t>
-        </is>
-      </c>
-      <c r="DU3" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV3" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW3" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ3" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK3" t="inlineStr">
-        <is>
-          <t>79.08</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr">
-        <is>
-          <t>219360</t>
-        </is>
-      </c>
-      <c r="EM3" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN3" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO3" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP3" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="EQ3" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ER3" t="inlineStr">
         <is>
           <t>210.0</t>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2207.66</t>
+          <t>2981.945</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,387 +3430,387 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>210.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.10931235303462698</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>219.4009568337635</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>210.5990431662365</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.04093913333733463</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.0006322047883784432</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.1194388933028725</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.0958841438292665</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.8440885667630521</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>307351.0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>184000.0</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>1017000.0</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>-833000.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>-506591.0</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>2026-05-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>14.71</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
         <is>
           <t>-0.71</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.1244041204927823</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>215.325</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>219.2623381336896</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>211.3876618663104</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.03657111931907204</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.0002231618605739172</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.06116199241267872</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.07499018369124305</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.7416038667766317</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-298081.0</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>172000.0</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1032000.0</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>-860000.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>48058.0</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>-1110023.0</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>2026-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>10.89</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,17 +3821,17 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -3840,283 +3840,283 @@
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="CL4" t="n">
-        <v>-1.31</v>
+        <v>-1.4</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>213.6</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>219.86</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>224.58</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>-0.002352941176470558</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>-0.002102312543798224</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>-0.002631101433496541</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>-0.0006396707086437914</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>-7.43</t>
+        </is>
+      </c>
+      <c r="DB4" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>-152.47</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>1113691511.663414</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DI4" t="n">
+        <v>446456989.4</v>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>402462830.4</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>367213800.2333333</t>
+        </is>
+      </c>
+      <c r="DL4" t="n">
+        <v>514612178.2</v>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>644200383.275</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>-5354496.075872992</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>28645776.31716985</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>-6.86</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>79.04</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>218840</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>214.05</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>215.32</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>220.44</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>224.72</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>226.44375</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>-0.00140977443609025</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>-0.001399580125962085</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>-0.00275955666138894</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>-0.001083483817196806</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>-0.0006527895259461625</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>-3.62</t>
-        </is>
-      </c>
-      <c r="DB4" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>-151.49</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>871548215.6657143</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DI4" t="n">
-        <v>418130651</v>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>371868657.7</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>365219125.0</t>
-        </is>
-      </c>
-      <c r="DL4" t="n">
-        <v>527411299.66</v>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>653166606.5875</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>-11536363.78606682</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>11185010.22767115</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR4" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS4" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT4" t="inlineStr">
-        <is>
-          <t>-5.97</t>
-        </is>
-      </c>
-      <c r="DU4" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV4" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE4" t="inlineStr">
-        <is>
-          <t>5.39</t>
-        </is>
-      </c>
-      <c r="EF4" t="inlineStr">
-        <is>
-          <t>4.27</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>19.01</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK4" t="inlineStr">
-        <is>
-          <t>79.08</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
-        <is>
-          <t>219360</t>
-        </is>
-      </c>
-      <c r="EM4" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN4" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO4" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP4" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
       <c r="EQ4" t="inlineStr">
         <is>
           <t>212.5</t>
@@ -4124,14 +4124,14 @@
       </c>
       <c r="ER4" t="inlineStr">
         <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ES4" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET4" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1661.585</t>
+          <t>2207.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.04757601939330377</t>
+          <t>0.1244041204927823</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.325</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>219.2134180594527</t>
+          <t>219.2623381336843</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>211.7865819405473</t>
+          <t>211.3876618663157</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.03446327665385303</t>
+          <t>0.0365711193190232</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0009272137227630539</t>
+          <t>-0.0008120649651972567</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.0002666812745690805</t>
+          <t>0.0002231618605752494</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.07580111770054776</t>
+          <t>0.06116199241285347</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.07499018369124305</t>
+          <t>0.0958841438292665</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6844365996151905</t>
+          <t>0.7416038667762083</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -4581,24 +4581,24 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>False</t>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>弱勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -4676,32 +4676,32 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-298081.0</t>
+          <t>307351.0</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>172000.0</t>
+          <t>184000.0</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1032000.0</t>
+          <t>1017000.0</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-860000.0</t>
+          <t>-833000.0</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>48058.0</t>
+          <t>19058.0</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-1110023.0</t>
+          <t>-506591.0</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,12 +4807,12 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -4822,95 +4822,95 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>-1.25</v>
+        <v>-1.31</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>212.8</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>214.35</t>
+          <t>214.05</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.32</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>221.05</t>
+          <t>220.44</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>224.97</t>
+          <t>224.72</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>226.5916666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>-0.002344116268166885</t>
+          <t>-0.00140977443609025</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>-0.001862630966239842</t>
+          <t>-0.001399580125962085</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>-0.0009272137227630539</t>
+          <t>-0.0008120649651972567</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>-0.002796950421798061</t>
+          <t>-0.00275955666138894</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>-0.00185791137485436</t>
+          <t>-0.001083483817196806</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>-0.000652363669775391</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="DB5" t="n">
-        <v>-2.2</v>
+        <v>-2.19</v>
       </c>
       <c r="DC5" t="n">
-        <v>-2.09</v>
+        <v>-2.11</v>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>-151.02</t>
+          <t>-151.49</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
@@ -4929,48 +4929,48 @@
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>871548215.6657143</t>
+          <t>1113691511.663414</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>353129823.0</t>
+          <t>467278976.0</t>
         </is>
       </c>
       <c r="DI5" t="n">
-        <v>366032679.6</v>
+        <v>418130651</v>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>349409181.6</t>
+          <t>371868657.7</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>361747717.0333334</t>
+          <t>365219125.0</t>
         </is>
       </c>
       <c r="DL5" t="n">
-        <v>541988911.52</v>
+        <v>527411299.66</v>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>663738938.0125</t>
+          <t>653166606.5875</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>-15667522.69765554</t>
+          <t>-11536363.78369896</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>3061425.806606054</t>
+          <t>11185010.22817957</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>353129823.0</t>
+          <t>467278976.0</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>218840</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="ES5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1493.082</t>
+          <t>1661.585</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5412,377 +5412,377 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-0.95</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.04757601939330377</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>219.2134180594471</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>211.7865819405529</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.03446327665380133</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.0009272137227630539</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.0002666812745708569</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.07580111770079268</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.0958841438292665</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.6844365996146634</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>307351.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>184000.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>1017000.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-833000.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>-506591.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>2026-05-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>8.19</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>-0.47</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.02818205226401916</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>215.7</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>219.1549735317831</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>212.2450264682169</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.03203498870452557</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.0015044555028354</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.0003340450614971457</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.08022388064267094</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.07499018369124305</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.6227152067319971</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>-298081.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>172000.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>1032000.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-860000.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>48058.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>-1110023.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>237.0</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>2026-05-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>-0.24</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,110 +5793,110 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-0.61</v>
+        <v>-0.14</v>
       </c>
       <c r="CL6" t="n">
-        <v>-1.11</v>
+        <v>-1.25</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>213.3</t>
+          <t>212.8</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>214.75</t>
+          <t>214.35</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>221.67</t>
+          <t>221.05</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>225.39</t>
+          <t>224.97</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>226.7395833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>-0.004201680672268782</t>
+          <t>-0.002344116268166885</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>-0.002091078066914442</t>
+          <t>-0.001862630966239842</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>-0.0015044555028354</t>
+          <t>-0.0009272137227630539</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>-0.002789149309460615</t>
+          <t>-0.002796950421798061</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>-0.001495182190718869</t>
+          <t>-0.00185791137485436</t>
         </is>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>-0.000661114528909934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="DB6" t="n">
-        <v>-2.19</v>
+        <v>-2.2</v>
       </c>
       <c r="DC6" t="n">
-        <v>-2.06</v>
+        <v>-2.09</v>
       </c>
       <c r="DD6" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>-150.35</t>
+          <t>-151.02</t>
         </is>
       </c>
       <c r="DF6" t="inlineStr">
@@ -5915,48 +5915,48 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>871548215.6657143</t>
+          <t>1113691511.663414</t>
         </is>
       </c>
       <c r="DH6" t="inlineStr">
         <is>
-          <t>316776227.0</t>
+          <t>353129823.0</t>
         </is>
       </c>
       <c r="DI6" t="n">
-        <v>345663307.4</v>
+        <v>366032679.6</v>
       </c>
       <c r="DJ6" t="inlineStr">
         <is>
-          <t>336188816.6</t>
+          <t>349409181.6</t>
         </is>
       </c>
       <c r="DK6" t="inlineStr">
         <is>
-          <t>367617217.2</t>
+          <t>361747717.0333334</t>
         </is>
       </c>
       <c r="DL6" t="n">
-        <v>561834701.02</v>
+        <v>541988911.52</v>
       </c>
       <c r="DM6" t="inlineStr">
         <is>
-          <t>700692145.4125</t>
+          <t>663738938.0125</t>
         </is>
       </c>
       <c r="DN6" t="inlineStr">
         <is>
-          <t>-19072786.06206674</t>
+          <t>-15667522.6949496</t>
         </is>
       </c>
       <c r="DO6" t="inlineStr">
         <is>
-          <t>3577234.96199137</t>
+          <t>3061425.80718708</t>
         </is>
       </c>
       <c r="DP6" t="inlineStr">
         <is>
-          <t>316776227.0</t>
+          <t>353129823.0</t>
         </is>
       </c>
       <c r="DQ6" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="DT6" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU6" t="inlineStr">
@@ -6021,22 +6021,22 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE6" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>218840</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6086,22 +6086,22 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2196.33</t>
+          <t>1493.082</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,359 +6388,359 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.02818205226401916</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>215.7</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>219.1549735317771</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>212.2450264682229</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.03203498870447023</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.0015044555028354</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.0003340450614949253</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.08022388064298025</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0958841438292665</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.622715206731353</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>307351.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>184000.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>1017000.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-833000.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>-506591.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.22693734286617706</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>216.025</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>219.228205631215</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>212.821794368785</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.02965587900673572</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>-0.001848215317084456</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.002463797900746689</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.04052320117702157</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.07499018369124305</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.563943123073434</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-298081.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>172000.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1032000.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-860000.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>48058.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>-1110023.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,12 +6779,12 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -6798,91 +6798,91 @@
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-0.79</v>
+        <v>-0.61</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.84</v>
+        <v>-1.11</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>214.2</t>
+          <t>213.3</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>215.2</t>
+          <t>214.75</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>216.02</t>
+          <t>215.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>222.29</t>
+          <t>221.67</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>225.39</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>226.8895833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>-0.004646840148698872</t>
+          <t>-0.004201680672268782</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>-0.002780352177942591</t>
+          <t>-0.002091078066914442</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>-0.001848215317084456</t>
+          <t>-0.0015044555028354</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>-0.002960305001121322</t>
+          <t>-0.002789149309460615</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>-0.001133943634704204</t>
+          <t>-0.001495182190718869</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>-0.0006973564684401579</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="DB7" t="n">
-        <v>-2.09</v>
+        <v>-2.19</v>
       </c>
       <c r="DC7" t="n">
-        <v>-2.03</v>
+        <v>-2.06</v>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>-149.59</t>
+          <t>-150.35</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
@@ -6901,48 +6901,48 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>871548215.6657143</t>
+          <t>1113691511.663414</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>467102515.0</t>
+          <t>316776227.0</t>
         </is>
       </c>
       <c r="DI7" t="n">
-        <v>402827322.8</v>
+        <v>345663307.4</v>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>328319392.3</t>
+          <t>336188816.6</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>376703314.4666666</t>
+          <t>367617217.2</t>
         </is>
       </c>
       <c r="DL7" t="n">
-        <v>582922481.98</v>
+        <v>561834701.02</v>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>734035263.775</t>
+          <t>700692145.4125</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>-23190971.70280458</t>
+          <t>-19072786.05897446</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>8081374.935327888</t>
+          <t>3577234.962655425</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>467102515.0</t>
+          <t>316776227.0</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>218840</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7077,19 +7077,19 @@
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ES7" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET7" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2277.177</t>
+          <t>2196.33</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.15575456569198345</t>
+          <t>0.22693734286617706</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7454,47 +7454,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>216.425</t>
+          <t>216.025</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>219.769673691905</t>
+          <t>219.2282056312086</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>213.0803263080951</t>
+          <t>212.8217943687914</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.03090838574014041</t>
+          <t>0.02965587900667599</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0023049441051054</t>
+          <t>-0.001848215317084456</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.005655295743209665</t>
+          <t>-0.002463797900748133</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.1812639188507745</t>
+          <t>-0.04052320117718478</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.07499018369124305</t>
+          <t>0.0958841438292665</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.5727216399708794</t>
+          <t>0.5639431230726679</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7539,142 +7539,142 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>307351.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>184000.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>1017000.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-833000.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-506591.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>-298081.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>172000.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1032000.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-860000.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>48058.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>-1110023.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,12 +7765,12 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -7784,91 +7784,91 @@
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-1.02</v>
+        <v>-0.79</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.57</v>
+        <v>-0.84</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
+          <t>214.2</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
           <t>215.2</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
-        <is>
-          <t>215.8</t>
-        </is>
-      </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>216.42</t>
+          <t>216.02</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>222.95</t>
+          <t>222.29</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>225.98</t>
+          <t>225.72</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>227.0479166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>-0.001855287569573316</t>
+          <t>-0.004646840148698872</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>-0.002080924855491273</t>
+          <t>-0.002780352177942591</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>-0.0023049441051054</t>
+          <t>-0.001848215317084456</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>-0.002817783343769698</t>
+          <t>-0.002960305001121322</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>-0.0008014149118443781</t>
+          <t>-0.001133943634704204</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>-0.0006418897233454457</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="DB8" t="n">
-        <v>-1.98</v>
+        <v>-2.09</v>
       </c>
       <c r="DC8" t="n">
-        <v>-2.02</v>
+        <v>-2.03</v>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>-149.26</t>
+          <t>-149.59</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -7887,48 +7887,48 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>871548215.6657143</t>
+          <t>1113691511.663414</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>486365714.0</t>
+          <t>467102515.0</t>
         </is>
       </c>
       <c r="DI8" t="n">
-        <v>358468671.4</v>
+        <v>402827322.8</v>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>310159857.5</t>
+          <t>328319392.3</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>389696834.5333334</t>
+          <t>376703314.4666666</t>
         </is>
       </c>
       <c r="DL8" t="n">
-        <v>598546724.48</v>
+        <v>582922481.98</v>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>767533169.1875</t>
+          <t>734035263.775</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>-28876852.90973775</t>
+          <t>-23190971.6992708</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>-1879147.921881616</t>
+          <t>8081374.936086774</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>486365714.0</t>
+          <t>467102515.0</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>218840</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8058,22 +8058,22 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
@@ -8098,42 +8098,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8143,22 +8143,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>963.738</t>
+          <t>2277.177</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.13009957206955292</t>
+          <t>0.15575456569198345</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -8440,47 +8440,47 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>216.925</t>
+          <t>216.425</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>221.0196049227907</t>
+          <t>219.7696736918988</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>212.8303950772093</t>
+          <t>213.0803263081012</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.03775134191808868</t>
+          <t>0.03090838574008341</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.00229964355524892</t>
+          <t>-0.0023049441051054</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.006071372308855794</t>
+          <t>-0.005655295743214994</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.1700107926473311</t>
+          <t>-0.1812639188512785</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.07499018369124305</t>
+          <t>0.0958841438292665</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.6749265067739033</t>
+          <t>0.5727216399701731</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -8525,24 +8525,24 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>False</t>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8620,32 +8620,32 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-298081.0</t>
+          <t>307351.0</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>172000.0</t>
+          <t>184000.0</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1032000.0</t>
+          <t>1017000.0</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-860000.0</t>
+          <t>-833000.0</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>48058.0</t>
+          <t>19058.0</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-1110023.0</t>
+          <t>-506591.0</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,12 +8751,12 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -8766,95 +8766,95 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-0.74</v>
+        <v>-1.02</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>215.6</t>
+          <t>215.2</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>216.25</t>
+          <t>215.8</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>216.92</t>
+          <t>216.42</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>223.58</t>
+          <t>222.95</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>226.16</t>
+          <t>225.98</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>227.19375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>-0.001389532190829157</t>
+          <t>-0.001855287569573316</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>-0.001385361348418379</t>
+          <t>-0.002080924855491273</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>-0.00229964355524892</t>
+          <t>-0.0023049441051054</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>-0.002498438475952436</t>
+          <t>-0.002817783343769698</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0008014149118443781</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>-0.0006597938144330406</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>7.96</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="DB9" t="n">
-        <v>-1.87</v>
+        <v>-1.98</v>
       </c>
       <c r="DC9" t="n">
-        <v>-2.03</v>
+        <v>-2.02</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-149.49</t>
+          <t>-149.26</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8873,48 +8873,48 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>871548215.6657143</t>
+          <t>1113691511.663414</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>206789119.0</t>
+          <t>486365714.0</t>
         </is>
       </c>
       <c r="DI9" t="n">
-        <v>325606664.4</v>
+        <v>358468671.4</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>288122102.2</t>
+          <t>310159857.5</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>382161641.2333333</t>
+          <t>389696834.5333334</t>
         </is>
       </c>
       <c r="DL9" t="n">
-        <v>606980317.38</v>
+        <v>598546724.48</v>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>803541390.0625</t>
+          <t>767533169.1875</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>-33785526.54389341</t>
+          <t>-28876852.90569945</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>-18105268.04211378</t>
+          <t>-1879147.921014369</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>206789119.0</t>
+          <t>486365714.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>218840</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9044,22 +9044,22 @@
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
@@ -9084,42 +9084,42 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1167.249</t>
+          <t>963.738</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.07424163374669263</t>
+          <t>0.13009957206955292</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>217.425</t>
+          <t>216.925</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>222.3696941260363</t>
+          <t>221.0196049227857</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>212.4803058739638</t>
+          <t>212.8303950772143</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.04548413591846603</t>
+          <t>0.0377513419180423</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.001950883635528977</t>
+          <t>-0.00229964355524892</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.004377368199252052</t>
+          <t>-0.006071372308859679</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.09877605190308758</t>
+          <t>-0.1700107926476495</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.07499018369124305</t>
+          <t>0.0958841438292665</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.7647884366923113</t>
+          <t>0.6749265067734521</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9511,142 +9511,142 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>307351.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>184000.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>1017000.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-833000.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>19058.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-506591.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-298081.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>172000.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>1032000.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-860000.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>48058.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>-1110023.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,12 +9737,12 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -9752,43 +9752,43 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>-0.42</v>
+        <v>-0.74</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0.7</v>
+        <v>-0.61</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>215.9</t>
+          <t>215.6</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>216.55</t>
+          <t>216.25</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>217.42</t>
+          <t>216.92</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>224.14</t>
+          <t>223.58</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
@@ -9798,49 +9798,49 @@
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>227.34375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>-0.001387604070305248</t>
+          <t>-0.001389532190829157</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.001385361348418379</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>-0.001950883635528977</t>
+          <t>-0.00229964355524892</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>-0.002181364911187367</t>
+          <t>-0.002498438475952436</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>0.0004423555432677695</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>-0.0006410549933605347</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>13.21</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="DB10" t="n">
-        <v>-1.8</v>
+        <v>-1.87</v>
       </c>
       <c r="DC10" t="n">
-        <v>-2.07</v>
+        <v>-2.03</v>
       </c>
       <c r="DD10" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="DE10" t="inlineStr">
         <is>
-          <t>-150.47</t>
+          <t>-149.49</t>
         </is>
       </c>
       <c r="DF10" t="inlineStr">
@@ -9859,48 +9859,48 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>871548215.6657143</t>
+          <t>1113691511.663414</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>251282962.0</t>
+          <t>206789119.0</t>
         </is>
       </c>
       <c r="DI10" t="n">
-        <v>332785683.6</v>
+        <v>325606664.4</v>
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
-          <t>309786618.9</t>
+          <t>288122102.2</t>
         </is>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>398030621.5</t>
+          <t>382161641.2333333</t>
         </is>
       </c>
       <c r="DL10" t="n">
-        <v>615894844.5599999</v>
+        <v>606980317.38</v>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>847038492.3375</t>
+          <t>803541390.0625</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>-36636482.63512607</t>
+          <t>-33785526.53927855</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>-10684187.74808425</t>
+          <t>-18105268.04112267</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>251282962.0</t>
+          <t>206789119.0</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>219360</t>
+          <t>218840</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10040,12 +10040,12 @@
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
@@ -10070,42 +10070,42 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/零售.xlsx
+++ b/Result/checksun_type/零售.xlsx
@@ -1433,7 +1433,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1565.939</t>
+          <t>1917.539</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.07804088643049134</t>
+          <t>0.06285389219119997</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1523,62 +1523,62 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>弱勢整理</t>
+          <t>空頭</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>214.45</t>
+          <t>214.375</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>219.4542087549558</t>
+          <t>219.3894527958856</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>209.4457912450442</t>
+          <t>209.3605472041144</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.04667016791751722</t>
+          <t>0.04678206690039047</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.001280707882174936</t>
+          <t>-0.000349731872231196</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0002036728923464626</t>
+          <t>-0.0002950773167744725</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0696132904526523</t>
+          <t>0.002397655458032277</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0958841438292665</t>
+          <t>0.07482042953939759</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.988611689761863</t>
+          <t>1.004951702009884</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,24 +1623,24 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ2" t="inlineStr">
         <is>
           <t>False</t>
@@ -1718,32 +1718,32 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>307351.0</t>
+          <t>1108436.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>184000.0</t>
+          <t>312000.0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1017000.0</t>
+          <t>1033000.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-833000.0</t>
+          <t>-721000.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>19058.0</t>
+          <t>13273.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-506591.0</t>
+          <t>400709.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,177 +1849,177 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>-0.43</v>
+        <v>0.9</v>
       </c>
       <c r="CL2" t="n">
-        <v>-1.42</v>
+        <v>-1.29</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>211.4</t>
+          <t>211.6</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>212.35</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>214.45</t>
+          <t>214.38</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>218.73</t>
+          <t>218.21</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>224.21</t>
+          <t>224.01</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
+          <t>225.85</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.0009460737937558861</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>-0.0007063809748057981</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>-0.000349731872231196</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>-0.002377360215791047</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>-0.0008641596744070057</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>-0.0006268667723736687</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>-153.90</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>407879940.0</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>415131914.8</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>390582297.2</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>325795920.4</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>484522306.52</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>626541939.95</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>-247091.7445604003</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>6910246.432334185</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>407879940.0</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>-0.001417099669343336</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>-0.002817562808170915</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>-0.001280707882174936</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>-0.002781070484179859</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>-0.0009468905784386639</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>-6.80</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>-154.32</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>329846967.0</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>404181891.4</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>374922599.4</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>330701942.7</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>492655844.94</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>630795391.725</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>-1548425.956954639</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>5333661.089675188</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>329846967.0</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>77.64</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>210.0</t>
-        </is>
-      </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1150.568</t>
+          <t>1565.939</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.0015658716132489568</t>
+          <t>0.07804088643049134</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -2509,62 +2509,62 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>弱勢整理</t>
+          <t>空頭</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>214.725</t>
+          <t>214.45</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>219.4095209832088</t>
+          <t>219.4542087549599</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>210.0404790167912</t>
+          <t>209.4457912450401</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.04363274870842971</t>
+          <t>0.04667016791755565</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.001279069767441854</t>
+          <t>-0.001280707882174936</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.903423927087424e-05</t>
+          <t>0.0002036728923451303</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.06579561293835745</t>
+          <t>0.06961329045252751</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0958841438292665</t>
+          <t>0.07482042953939759</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.9130721947443678</t>
+          <t>0.9886116897618522</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2609,24 +2609,24 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>False</t>
@@ -2704,32 +2704,32 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>307351.0</t>
+          <t>1108436.0</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>184000.0</t>
+          <t>312000.0</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1017000.0</t>
+          <t>1033000.0</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-833000.0</t>
+          <t>-721000.0</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>19058.0</t>
+          <t>13273.0</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-506591.0</t>
+          <t>400709.0</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,177 +2835,177 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="CL3" t="n">
-        <v>-1.41</v>
+        <v>-1.42</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>211.7</t>
+          <t>211.4</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>212.95</t>
+          <t>212.35</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>214.45</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>219.34</t>
+          <t>218.73</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>224.42</t>
+          <t>224.21</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
+          <t>225.9916666666667</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>-0.001417099669343336</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>-0.002817562808170915</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>-0.001280707882174936</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>-0.002781070484179859</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>-0.0009468905784386639</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>-0.0006540945396923403</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>-6.80</t>
+        </is>
+      </c>
+      <c r="DB3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>-154.32</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>329846967.0</t>
+        </is>
+      </c>
+      <c r="DI3" t="n">
+        <v>404181891.4</v>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>374922599.4</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>330701942.7</t>
+        </is>
+      </c>
+      <c r="DL3" t="n">
+        <v>492655844.94</v>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>630795391.725</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>-1548425.958541234</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>5333661.089334548</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>329846967.0</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>-0.001415094339622724</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>-0.003043071161048738</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>-0.001279069767441854</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>-0.002365141453652408</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>-0.0007235688642752702</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>-6.95</t>
-        </is>
-      </c>
-      <c r="DB3" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>-153.39</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>242656285.0</t>
-        </is>
-      </c>
-      <c r="DI3" t="n">
-        <v>401567743.4</v>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>402197533.1</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>360892111.8</t>
-        </is>
-      </c>
-      <c r="DL3" t="n">
-        <v>499527332.66</v>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>636367710.4625</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>-2799714.510887335</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>11251584.09653378</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>242656285.0</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR3" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>77.64</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="EP3" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="EQ3" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2981.945</t>
+          <t>1150.568</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.10931235303462698</t>
+          <t>-0.0015658716132489568</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -3495,62 +3495,62 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>弱勢整理</t>
+          <t>空頭</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.725</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>219.4009568337635</t>
+          <t>219.4095209832132</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>210.5990431662365</t>
+          <t>210.0404790167868</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.04093913333733463</t>
+          <t>0.04363274870847074</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.001509346336932449</t>
+          <t>-0.001279069767441854</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0006322047883784432</t>
+          <t>3.903423926954197e-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.1194388933028725</t>
+          <t>0.065795612938224</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.0958841438292665</t>
+          <t>0.07482042953939759</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.8440885667630521</t>
+          <t>0.9130721947444821</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -3690,32 +3690,32 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>307351.0</t>
+          <t>1108436.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>184000.0</t>
+          <t>312000.0</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1017000.0</t>
+          <t>1033000.0</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-833000.0</t>
+          <t>-721000.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>19058.0</t>
+          <t>13273.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-506591.0</t>
+          <t>400709.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,307 +3821,307 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>-0.71</v>
+        <v>-0.33</v>
       </c>
       <c r="CL4" t="n">
-        <v>-1.4</v>
+        <v>-1.41</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
+          <t>211.7</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>212.95</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>214.72</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>219.34</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>224.42</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>226.1395833333333</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>-0.001415094339622724</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>-0.003043071161048738</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>-0.001279069767441854</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>-0.002365141453652408</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>-0.0007235688642752702</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>-0.0006536669796902705</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>-6.95</t>
+        </is>
+      </c>
+      <c r="DB4" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>-153.39</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DI4" t="n">
+        <v>401567743.4</v>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>402197533.1</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>360892111.8</t>
+        </is>
+      </c>
+      <c r="DL4" t="n">
+        <v>499527332.66</v>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>636367710.4625</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>-2799714.512700467</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>11251584.0961445</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>-6.64</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>19.23</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>77.64</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>221959</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>213.6</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>215.0</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>219.86</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>224.58</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CU4" t="inlineStr">
-        <is>
-          <t>-0.002352941176470558</t>
-        </is>
-      </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>-0.002102312543798224</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
-        <is>
-          <t>-0.001509346336932449</t>
-        </is>
-      </c>
-      <c r="CX4" t="inlineStr">
-        <is>
-          <t>-0.002631101433496541</t>
-        </is>
-      </c>
-      <c r="CY4" t="inlineStr">
-        <is>
-          <t>-0.0006396707086437914</t>
-        </is>
-      </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA4" t="inlineStr">
-        <is>
-          <t>-7.43</t>
-        </is>
-      </c>
-      <c r="DB4" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>-152.47</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DI4" t="n">
-        <v>446456989.4</v>
-      </c>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>402462830.4</t>
-        </is>
-      </c>
-      <c r="DK4" t="inlineStr">
-        <is>
-          <t>367213800.2333333</t>
-        </is>
-      </c>
-      <c r="DL4" t="n">
-        <v>514612178.2</v>
-      </c>
-      <c r="DM4" t="inlineStr">
-        <is>
-          <t>644200383.275</t>
-        </is>
-      </c>
-      <c r="DN4" t="inlineStr">
-        <is>
-          <t>-5354496.075872992</t>
-        </is>
-      </c>
-      <c r="DO4" t="inlineStr">
-        <is>
-          <t>28645776.31716985</t>
-        </is>
-      </c>
-      <c r="DP4" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR4" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS4" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT4" t="inlineStr">
-        <is>
-          <t>-6.86</t>
-        </is>
-      </c>
-      <c r="DU4" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV4" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB4" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="EE4" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="EF4" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK4" t="inlineStr">
-        <is>
-          <t>79.04</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
-        <is>
-          <t>218840</t>
-        </is>
-      </c>
-      <c r="EM4" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN4" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO4" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP4" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="EQ4" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ER4" t="inlineStr">
         <is>
           <t>210.0</t>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2207.66</t>
+          <t>2981.945</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,359 +4416,359 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>210.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.10931235303462698</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>219.4009568337682</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>210.5990431662318</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.04093913333737826</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.0006322047883757786</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.1194388933025705</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.07482042953939759</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.8440885667632837</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>1108436.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>312000.0</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>1033000.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-721000.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>13273.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>400709.0</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.1244041204927823</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>215.325</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>219.2623381336843</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>211.3876618663157</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.0365711193190232</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.0002231618605752494</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.06116199241285347</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.0958841438292665</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0.7416038667762083</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>307351.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>184000.0</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>1017000.0</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>-833000.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>19058.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>-506591.0</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,17 +4807,17 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -4826,283 +4826,283 @@
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="CL5" t="n">
-        <v>-1.31</v>
+        <v>-1.4</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>213.6</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>219.86</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>224.58</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>226.2875</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>-0.002352941176470558</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>-0.002102312543798224</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>-0.002631101433496541</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>-0.0006396707086437914</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>-0.0006900168364107895</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>-7.43</t>
+        </is>
+      </c>
+      <c r="DB5" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>-152.47</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>446456989.4</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>402462830.4</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>367213800.2333333</t>
+        </is>
+      </c>
+      <c r="DL5" t="n">
+        <v>514612178.2</v>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>644200383.275</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>-5354496.077945007</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>28645776.31672496</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>-6.86</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>19.23</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>77.64</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>221959</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>214.05</t>
-        </is>
-      </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>215.32</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>220.44</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>224.72</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>-0.00140977443609025</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>-0.001399580125962085</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>-0.00275955666138894</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>-0.001083483817196806</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>-3.62</t>
-        </is>
-      </c>
-      <c r="DB5" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>-151.49</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH5" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DI5" t="n">
-        <v>418130651</v>
-      </c>
-      <c r="DJ5" t="inlineStr">
-        <is>
-          <t>371868657.7</t>
-        </is>
-      </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>365219125.0</t>
-        </is>
-      </c>
-      <c r="DL5" t="n">
-        <v>527411299.66</v>
-      </c>
-      <c r="DM5" t="inlineStr">
-        <is>
-          <t>653166606.5875</t>
-        </is>
-      </c>
-      <c r="DN5" t="inlineStr">
-        <is>
-          <t>-11536363.78369896</t>
-        </is>
-      </c>
-      <c r="DO5" t="inlineStr">
-        <is>
-          <t>11185010.22817957</t>
-        </is>
-      </c>
-      <c r="DP5" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR5" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS5" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT5" t="inlineStr">
-        <is>
-          <t>-5.97</t>
-        </is>
-      </c>
-      <c r="DU5" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV5" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW5" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ5" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>5.39</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>18.96</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK5" t="inlineStr">
-        <is>
-          <t>79.04</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
-        <is>
-          <t>218840</t>
-        </is>
-      </c>
-      <c r="EM5" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN5" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO5" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP5" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
       <c r="EQ5" t="inlineStr">
         <is>
           <t>212.5</t>
@@ -5110,14 +5110,14 @@
       </c>
       <c r="ER5" t="inlineStr">
         <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ES5" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET5" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1661.585</t>
+          <t>2207.66</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.04757601939330377</t>
+          <t>0.1244041204927823</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -5482,47 +5482,47 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.325</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>219.2134180594471</t>
+          <t>219.2623381336896</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>211.7865819405529</t>
+          <t>211.3876618663104</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.03446327665380133</t>
+          <t>0.03657111931907204</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-0.0009272137227630539</t>
+          <t>-0.0008120649651972567</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0002666812745708569</t>
+          <t>0.0002231618605739172</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.07580111770079268</t>
+          <t>0.06116199241267872</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.0958841438292665</t>
+          <t>0.07482042953939759</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.6844365996146634</t>
+          <t>0.7416038667766317</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>弱勢</t>
+          <t>盤整</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -5662,32 +5662,32 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>307351.0</t>
+          <t>1108436.0</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>184000.0</t>
+          <t>312000.0</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1017000.0</t>
+          <t>1033000.0</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-833000.0</t>
+          <t>-721000.0</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>19058.0</t>
+          <t>13273.0</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-506591.0</t>
+          <t>400709.0</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,12 +5793,12 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -5808,162 +5808,162 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>-1.25</v>
+        <v>-1.31</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>212.8</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>214.35</t>
+          <t>214.05</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.32</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>221.05</t>
+          <t>220.44</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>224.97</t>
+          <t>224.72</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
+          <t>226.44375</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>-0.00140977443609025</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>-0.001399580125962085</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>-0.0008120649651972567</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>-0.00275955666138894</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>-0.001083483817196806</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>-0.0006527895259461625</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>-3.62</t>
+        </is>
+      </c>
+      <c r="DB6" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>-151.49</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>467278976.0</t>
+        </is>
+      </c>
+      <c r="DI6" t="n">
+        <v>418130651</v>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>371868657.7</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>365219125.0</t>
+        </is>
+      </c>
+      <c r="DL6" t="n">
+        <v>527411299.66</v>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>653166606.5875</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>-11536363.78606682</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>11185010.22767115</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>467278976.0</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>-0.002344116268166885</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>-0.001862630966239842</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>-0.0009272137227630539</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>-0.002796950421798061</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>-0.00185791137485436</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>-5.27</t>
-        </is>
-      </c>
-      <c r="DB6" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>-151.02</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>353129823.0</t>
-        </is>
-      </c>
-      <c r="DI6" t="n">
-        <v>366032679.6</v>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>349409181.6</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>361747717.0333334</t>
-        </is>
-      </c>
-      <c r="DL6" t="n">
-        <v>541988911.52</v>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>663738938.0125</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>-15667522.6949496</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>3061425.80718708</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>353129823.0</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="EC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED6" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="EF6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EG6" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="EI6" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="EK6" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>77.64</t>
         </is>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="EM6" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="ES6" t="inlineStr">
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1493.082</t>
+          <t>1661.585</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.02818205226401916</t>
+          <t>0.04757601939330377</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -6468,47 +6468,47 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>219.1549735317771</t>
+          <t>219.2134180594527</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>212.2450264682229</t>
+          <t>211.7865819405473</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.03203498870447023</t>
+          <t>0.03446327665385303</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0015044555028354</t>
+          <t>-0.0009272137227630539</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.0003340450614949253</t>
+          <t>0.0002666812745690805</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.08022388064298025</t>
+          <t>0.07580111770054776</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0958841438292665</t>
+          <t>0.07482042953939759</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0.622715206731353</t>
+          <t>0.6844365996151905</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -6563,14 +6563,14 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AQ7" t="inlineStr">
         <is>
           <t>False</t>
@@ -6633,14 +6633,14 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
           <t>弱勢</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
       <c r="BE7" t="inlineStr">
         <is>
           <t>83.3</t>
@@ -6648,32 +6648,32 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>307351.0</t>
+          <t>1108436.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>184000.0</t>
+          <t>312000.0</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1017000.0</t>
+          <t>1033000.0</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-833000.0</t>
+          <t>-721000.0</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>19058.0</t>
+          <t>13273.0</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-506591.0</t>
+          <t>400709.0</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,177 +6779,177 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-0.61</v>
+        <v>-0.14</v>
       </c>
       <c r="CL7" t="n">
-        <v>-1.11</v>
+        <v>-1.25</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>213.3</t>
+          <t>212.8</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>214.75</t>
+          <t>214.35</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>221.67</t>
+          <t>221.05</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>225.39</t>
+          <t>224.97</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
+          <t>226.5916666666667</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>-0.002344116268166885</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>-0.001862630966239842</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>-0.0009272137227630539</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>-0.002796950421798061</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>-0.00185791137485436</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>-0.000652363669775391</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>-5.27</t>
+        </is>
+      </c>
+      <c r="DB7" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>-151.02</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>353129823.0</t>
+        </is>
+      </c>
+      <c r="DI7" t="n">
+        <v>366032679.6</v>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>349409181.6</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>361747717.0333334</t>
+        </is>
+      </c>
+      <c r="DL7" t="n">
+        <v>541988911.52</v>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>663738938.0125</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>-15667522.69765554</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>3061425.806606054</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>353129823.0</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
-        <is>
-          <t>-0.004201680672268782</t>
-        </is>
-      </c>
-      <c r="CV7" t="inlineStr">
-        <is>
-          <t>-0.002091078066914442</t>
-        </is>
-      </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>-0.0015044555028354</t>
-        </is>
-      </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>-0.002789149309460615</t>
-        </is>
-      </c>
-      <c r="CY7" t="inlineStr">
-        <is>
-          <t>-0.001495182190718869</t>
-        </is>
-      </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA7" t="inlineStr">
-        <is>
-          <t>-6.02</t>
-        </is>
-      </c>
-      <c r="DB7" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="DD7" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>-150.35</t>
-        </is>
-      </c>
-      <c r="DF7" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG7" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH7" t="inlineStr">
-        <is>
-          <t>316776227.0</t>
-        </is>
-      </c>
-      <c r="DI7" t="n">
-        <v>345663307.4</v>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>336188816.6</t>
-        </is>
-      </c>
-      <c r="DK7" t="inlineStr">
-        <is>
-          <t>367617217.2</t>
-        </is>
-      </c>
-      <c r="DL7" t="n">
-        <v>561834701.02</v>
-      </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>700692145.4125</t>
-        </is>
-      </c>
-      <c r="DN7" t="inlineStr">
-        <is>
-          <t>-19072786.05897446</t>
-        </is>
-      </c>
-      <c r="DO7" t="inlineStr">
-        <is>
-          <t>3577234.962655425</t>
-        </is>
-      </c>
-      <c r="DP7" t="inlineStr">
-        <is>
-          <t>316776227.0</t>
-        </is>
-      </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR7" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="DT7" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU7" t="inlineStr">
@@ -7007,22 +7007,22 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>77.64</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7072,22 +7072,22 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2196.33</t>
+          <t>1493.082</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,359 +7374,359 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.02818205226401916</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>215.7</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>219.1549735317831</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>212.2450264682169</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.03203498870452557</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>-0.0015044555028354</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-0.0003340450614971457</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.08022388064267094</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.07482042953939759</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.6227152067319971</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>1108436.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>312000.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>1033000.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-721000.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>13273.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>400709.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.95</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.22693734286617706</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>216.025</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>219.2282056312086</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>212.8217943687914</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.02965587900667599</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>-0.001848215317084456</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-0.002463797900748133</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.04052320117718478</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0.0958841438292665</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0.5639431230726679</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>307351.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>184000.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1017000.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-833000.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>19058.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>-506591.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,12 +7765,12 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -7784,158 +7784,158 @@
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-0.79</v>
+        <v>-0.61</v>
       </c>
       <c r="CL8" t="n">
-        <v>-0.84</v>
+        <v>-1.11</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>214.2</t>
+          <t>213.3</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>215.2</t>
+          <t>214.75</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>216.02</t>
+          <t>215.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>222.29</t>
+          <t>221.67</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>225.39</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
+          <t>226.7395833333333</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>-0.004201680672268782</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>-0.002091078066914442</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>-0.0015044555028354</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>-0.002789149309460615</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>-0.001495182190718869</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>-0.000661114528909934</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>-6.02</t>
+        </is>
+      </c>
+      <c r="DB8" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>-150.35</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>316776227.0</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>345663307.4</v>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>336188816.6</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>367617217.2</t>
+        </is>
+      </c>
+      <c r="DL8" t="n">
+        <v>561834701.02</v>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>700692145.4125</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>-19072786.06206674</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>3577234.96199137</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>316776227.0</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
-        <is>
-          <t>-0.004646840148698872</t>
-        </is>
-      </c>
-      <c r="CV8" t="inlineStr">
-        <is>
-          <t>-0.002780352177942591</t>
-        </is>
-      </c>
-      <c r="CW8" t="inlineStr">
-        <is>
-          <t>-0.001848215317084456</t>
-        </is>
-      </c>
-      <c r="CX8" t="inlineStr">
-        <is>
-          <t>-0.002960305001121322</t>
-        </is>
-      </c>
-      <c r="CY8" t="inlineStr">
-        <is>
-          <t>-0.001133943634704204</t>
-        </is>
-      </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA8" t="inlineStr">
-        <is>
-          <t>-2.73</t>
-        </is>
-      </c>
-      <c r="DB8" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="DD8" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE8" t="inlineStr">
-        <is>
-          <t>-149.59</t>
-        </is>
-      </c>
-      <c r="DF8" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG8" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH8" t="inlineStr">
-        <is>
-          <t>467102515.0</t>
-        </is>
-      </c>
-      <c r="DI8" t="n">
-        <v>402827322.8</v>
-      </c>
-      <c r="DJ8" t="inlineStr">
-        <is>
-          <t>328319392.3</t>
-        </is>
-      </c>
-      <c r="DK8" t="inlineStr">
-        <is>
-          <t>376703314.4666666</t>
-        </is>
-      </c>
-      <c r="DL8" t="n">
-        <v>582922481.98</v>
-      </c>
-      <c r="DM8" t="inlineStr">
-        <is>
-          <t>734035263.775</t>
-        </is>
-      </c>
-      <c r="DN8" t="inlineStr">
-        <is>
-          <t>-23190971.6992708</t>
-        </is>
-      </c>
-      <c r="DO8" t="inlineStr">
-        <is>
-          <t>8081374.936086774</t>
-        </is>
-      </c>
-      <c r="DP8" t="inlineStr">
-        <is>
-          <t>467102515.0</t>
-        </is>
-      </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>77.64</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8063,19 +8063,19 @@
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ES8" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET8" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -8098,42 +8098,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8143,22 +8143,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8335,7 +8335,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8345,12 +8345,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2277.177</t>
+          <t>2196.33</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.15575456569198345</t>
+          <t>0.22693734286617706</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -8440,47 +8440,47 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>216.425</t>
+          <t>216.025</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>219.7696736918988</t>
+          <t>219.228205631215</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>213.0803263081012</t>
+          <t>212.821794368785</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.03090838574008341</t>
+          <t>0.02965587900673572</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.0023049441051054</t>
+          <t>-0.001848215317084456</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.005655295743214994</t>
+          <t>-0.002463797900746689</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.1812639188512785</t>
+          <t>-0.04052320117702157</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0958841438292665</t>
+          <t>0.07482042953939759</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.5727216399701731</t>
+          <t>0.563943123073434</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -8540,127 +8540,127 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>1108436.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>312000.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>1033000.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-721000.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>13273.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>400709.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>307351.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>184000.0</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1017000.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>-833000.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>19058.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>-506591.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,12 +8751,12 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -8770,158 +8770,158 @@
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-1.02</v>
+        <v>-0.79</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.57</v>
+        <v>-0.84</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
+          <t>214.2</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
           <t>215.2</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>215.8</t>
-        </is>
-      </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>216.42</t>
+          <t>216.02</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>222.95</t>
+          <t>222.29</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>225.98</t>
+          <t>225.72</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
+          <t>226.8895833333333</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>-0.004646840148698872</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>-0.002780352177942591</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>-0.001848215317084456</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>-0.002960305001121322</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>-0.001133943634704204</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>-0.0006973564684401579</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>-2.73</t>
+        </is>
+      </c>
+      <c r="DB9" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>-149.59</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>467102515.0</t>
+        </is>
+      </c>
+      <c r="DI9" t="n">
+        <v>402827322.8</v>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>328319392.3</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>376703314.4666666</t>
+        </is>
+      </c>
+      <c r="DL9" t="n">
+        <v>582922481.98</v>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>734035263.775</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>-23190971.70280458</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>8081374.935327888</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>467102515.0</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>-0.001855287569573316</t>
-        </is>
-      </c>
-      <c r="CV9" t="inlineStr">
-        <is>
-          <t>-0.002080924855491273</t>
-        </is>
-      </c>
-      <c r="CW9" t="inlineStr">
-        <is>
-          <t>-0.0023049441051054</t>
-        </is>
-      </c>
-      <c r="CX9" t="inlineStr">
-        <is>
-          <t>-0.002817783343769698</t>
-        </is>
-      </c>
-      <c r="CY9" t="inlineStr">
-        <is>
-          <t>-0.0008014149118443781</t>
-        </is>
-      </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="DB9" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>-149.26</t>
-        </is>
-      </c>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG9" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH9" t="inlineStr">
-        <is>
-          <t>486365714.0</t>
-        </is>
-      </c>
-      <c r="DI9" t="n">
-        <v>358468671.4</v>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>310159857.5</t>
-        </is>
-      </c>
-      <c r="DK9" t="inlineStr">
-        <is>
-          <t>389696834.5333334</t>
-        </is>
-      </c>
-      <c r="DL9" t="n">
-        <v>598546724.48</v>
-      </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>767533169.1875</t>
-        </is>
-      </c>
-      <c r="DN9" t="inlineStr">
-        <is>
-          <t>-28876852.90569945</t>
-        </is>
-      </c>
-      <c r="DO9" t="inlineStr">
-        <is>
-          <t>-1879147.921014369</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>486365714.0</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>77.64</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9044,22 +9044,22 @@
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES9" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET9" t="inlineStr">
@@ -9084,42 +9084,42 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>963.738</t>
+          <t>2277.177</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.13009957206955292</t>
+          <t>0.15575456569198345</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>216.925</t>
+          <t>216.425</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>221.0196049227857</t>
+          <t>219.769673691905</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>212.8303950772143</t>
+          <t>213.0803263080951</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0377513419180423</t>
+          <t>0.03090838574014041</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.00229964355524892</t>
+          <t>-0.0023049441051054</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.006071372308859679</t>
+          <t>-0.005655295743209665</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.1700107926476495</t>
+          <t>-0.1812639188507745</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0958841438292665</t>
+          <t>0.07482042953939759</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.6749265067734521</t>
+          <t>0.5727216399708794</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -9521,132 +9521,132 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>1108436.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>312000.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>1033000.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-721000.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>13273.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>400709.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>307351.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>184000.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>1017000.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-833000.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>19058.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>-506591.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,12 +9737,12 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>47</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -9752,162 +9752,162 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>-0.74</v>
+        <v>-1.02</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0.61</v>
+        <v>-0.57</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>215.6</t>
+          <t>215.2</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>216.25</t>
+          <t>215.8</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>216.92</t>
+          <t>216.42</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>223.58</t>
+          <t>222.95</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>226.16</t>
+          <t>225.98</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
+          <t>227.0479166666667</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>-0.001855287569573316</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>-0.002080924855491273</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>-0.0023049441051054</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>-0.002817783343769698</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>-0.0008014149118443781</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>-0.0006418897233454457</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="DB10" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>-149.26</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>869739959.7826705</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>486365714.0</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>358468671.4</v>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>310159857.5</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>389696834.5333334</t>
+        </is>
+      </c>
+      <c r="DL10" t="n">
+        <v>598546724.48</v>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>767533169.1875</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>-28876852.90973775</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>-1879147.921881616</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>486365714.0</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
-        <is>
-          <t>-0.001389532190829157</t>
-        </is>
-      </c>
-      <c r="CV10" t="inlineStr">
-        <is>
-          <t>-0.001385361348418379</t>
-        </is>
-      </c>
-      <c r="CW10" t="inlineStr">
-        <is>
-          <t>-0.00229964355524892</t>
-        </is>
-      </c>
-      <c r="CX10" t="inlineStr">
-        <is>
-          <t>-0.002498438475952436</t>
-        </is>
-      </c>
-      <c r="CY10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DA10" t="inlineStr">
-        <is>
-          <t>7.96</t>
-        </is>
-      </c>
-      <c r="DB10" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="DD10" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE10" t="inlineStr">
-        <is>
-          <t>-149.49</t>
-        </is>
-      </c>
-      <c r="DF10" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="DG10" t="inlineStr">
-        <is>
-          <t>1113691511.663414</t>
-        </is>
-      </c>
-      <c r="DH10" t="inlineStr">
-        <is>
-          <t>206789119.0</t>
-        </is>
-      </c>
-      <c r="DI10" t="n">
-        <v>325606664.4</v>
-      </c>
-      <c r="DJ10" t="inlineStr">
-        <is>
-          <t>288122102.2</t>
-        </is>
-      </c>
-      <c r="DK10" t="inlineStr">
-        <is>
-          <t>382161641.2333333</t>
-        </is>
-      </c>
-      <c r="DL10" t="n">
-        <v>606980317.38</v>
-      </c>
-      <c r="DM10" t="inlineStr">
-        <is>
-          <t>803541390.0625</t>
-        </is>
-      </c>
-      <c r="DN10" t="inlineStr">
-        <is>
-          <t>-33785526.53927855</t>
-        </is>
-      </c>
-      <c r="DO10" t="inlineStr">
-        <is>
-          <t>-18105268.04112267</t>
-        </is>
-      </c>
-      <c r="DP10" t="inlineStr">
-        <is>
-          <t>206789119.0</t>
-        </is>
-      </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
           <t>226.0</t>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.23</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>77.64</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>218840</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10030,22 +10030,22 @@
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
@@ -10070,42 +10070,42 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/零售.xlsx
+++ b/Result/checksun_type/零售.xlsx
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1917.539</t>
+          <t>1914.231</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.06285389219119997</t>
+          <t>-0.018394066007030804</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1538,47 +1538,47 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>214.375</t>
+          <t>214.175</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>219.3894527958856</t>
+          <t>219.0661843361854</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>209.3605472041144</t>
+          <t>209.2838156638147</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.04678206690039047</t>
+          <t>0.04567465237479021</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.000349731872231196</t>
+          <t>-0.0009329446064139102</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.0002950773167744725</t>
+          <t>-0.0014734913441663</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.002397655458032277</t>
+          <t>-0.02367177422751876</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.07482042953939759</t>
+          <t>0.09535589080595058</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1.004951702009884</t>
+          <t>0.9965998239007965</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1623,22 +1623,22 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1108436.0</t>
+          <t>1555506.0</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>312000.0</t>
+          <t>192000.0</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1033000.0</t>
+          <t>883000.0</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-721000.0</t>
+          <t>-691000.0</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>13273.0</t>
+          <t>14905.0</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>400709.0</t>
+          <t>879411.0</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.44</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1849,110 +1849,110 @@
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>0.9</v>
+        <v>0.61</v>
       </c>
       <c r="CL2" t="n">
-        <v>-1.29</v>
+        <v>-1.16</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>211.6</t>
+          <t>211.7</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>212.2</t>
+          <t>212.1</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>214.38</t>
+          <t>214.18</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>218.21</t>
+          <t>217.72</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>224.01</t>
+          <t>223.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>225.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>0.0009460737937558861</t>
+          <t>0.0004725897920605515</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>-0.0007063809748057981</t>
+          <t>-0.0004712535344014723</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>-0.000349731872231196</t>
+          <t>-0.0009329446064139102</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>-0.002377360215791047</t>
+          <t>-0.002245543283992513</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>-0.0008641596744070057</t>
+          <t>-0.0009486077785836322</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>-0.0006268667723736687</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>-2.14</v>
+        <v>-1.97</v>
       </c>
       <c r="DC2" t="n">
-        <v>-2.21</v>
+        <v>-2.16</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>-153.90</t>
+          <t>-152.73</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
@@ -1971,48 +1971,48 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>869739959.7826705</t>
+          <t>1108834326.963768</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>407879940.0</t>
+          <t>406750587.0</t>
         </is>
       </c>
       <c r="DI2" t="n">
-        <v>415131914.8</v>
+        <v>403026237</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>390582297.2</t>
+          <t>410578444.0</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>325795920.4</t>
+          <t>329080732.6</t>
         </is>
       </c>
       <c r="DL2" t="n">
-        <v>484522306.52</v>
+        <v>480983763.3</v>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>626541939.95</t>
+          <t>626861142.9625</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>-247091.7445604003</t>
+          <t>984214.4537600467</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>6910246.432334185</t>
+          <t>7756398.536886513</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>407879940.0</t>
+          <t>406750587.0</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
@@ -2077,22 +2077,22 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.40</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>77.83</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>221439</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
@@ -2182,42 +2182,42 @@
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK2" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1565.939</t>
+          <t>1917.539</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.07804088643049134</t>
+          <t>0.06285389219119997</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2524,47 +2524,47 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>214.45</t>
+          <t>214.375</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>219.4542087549599</t>
+          <t>219.3894527958815</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>209.4457912450401</t>
+          <t>209.3605472041185</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.04667016791755565</t>
+          <t>0.04678206690035202</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.001280707882174936</t>
+          <t>-0.000349731872231196</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0002036728923451303</t>
+          <t>-0.0002950773167745835</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.06961329045252751</t>
+          <t>0.002397655458034054</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.07482042953939759</t>
+          <t>0.09535589080595058</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.9886116897618522</t>
+          <t>1.004951702009919</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -2609,24 +2609,24 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>False</t>
@@ -2704,32 +2704,32 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1108436.0</t>
+          <t>1555506.0</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>312000.0</t>
+          <t>192000.0</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1033000.0</t>
+          <t>883000.0</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-721000.0</t>
+          <t>-691000.0</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>13273.0</t>
+          <t>14905.0</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>400709.0</t>
+          <t>879411.0</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -2835,110 +2835,110 @@
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="CK3" t="n">
-        <v>-0.43</v>
+        <v>0.9</v>
       </c>
       <c r="CL3" t="n">
-        <v>-1.42</v>
+        <v>-1.29</v>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>211.4</t>
+          <t>211.6</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>212.35</t>
+          <t>212.2</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>214.45</t>
+          <t>214.38</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>218.73</t>
+          <t>218.21</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>224.21</t>
+          <t>224.01</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>225.9916666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>-0.001417099669343336</t>
+          <t>0.0009460737937558861</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>-0.002817562808170915</t>
+          <t>-0.0007063809748057981</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>-0.001280707882174936</t>
+          <t>-0.000349731872231196</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>-0.002781070484179859</t>
+          <t>-0.002377360215791047</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>-0.0009468905784386639</t>
+          <t>-0.0008641596744070057</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>-0.0006540945396923403</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>-6.80</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="DB3" t="n">
-        <v>-2.38</v>
+        <v>-2.14</v>
       </c>
       <c r="DC3" t="n">
-        <v>-2.23</v>
+        <v>-2.21</v>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>-154.32</t>
+          <t>-153.90</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
@@ -2957,48 +2957,48 @@
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>869739959.7826705</t>
+          <t>1108834326.963768</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>329846967.0</t>
+          <t>407879940.0</t>
         </is>
       </c>
       <c r="DI3" t="n">
-        <v>404181891.4</v>
+        <v>415131914.8</v>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>374922599.4</t>
+          <t>390582297.2</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>330701942.7</t>
+          <t>325795920.4</t>
         </is>
       </c>
       <c r="DL3" t="n">
-        <v>492655844.94</v>
+        <v>484522306.52</v>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>630795391.725</t>
+          <t>626541939.95</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>-1548425.958541234</t>
+          <t>-247091.7431720381</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>5333661.089334548</t>
+          <t>6910246.432632267</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>329846967.0</t>
+          <t>407879940.0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="EK3" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>77.83</t>
         </is>
       </c>
       <c r="EL3" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>221439</t>
         </is>
       </c>
       <c r="EM3" t="inlineStr">
@@ -3128,22 +3128,22 @@
       </c>
       <c r="EP3" t="inlineStr">
         <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="EQ3" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
-      <c r="ER3" t="inlineStr">
-        <is>
-          <t>210.0</t>
-        </is>
-      </c>
       <c r="ES3" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="ET3" t="inlineStr">
@@ -3168,42 +3168,42 @@
       </c>
       <c r="EX3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF3" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK3" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1150.568</t>
+          <t>1565.939</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.0015658716132489568</t>
+          <t>0.07804088643049134</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -3510,47 +3510,47 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>214.725</t>
+          <t>214.45</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>219.4095209832132</t>
+          <t>219.4542087549558</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>210.0404790167868</t>
+          <t>209.4457912450442</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.04363274870847074</t>
+          <t>0.04667016791751722</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.001279069767441854</t>
+          <t>-0.001280707882174936</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.903423926954197e-05</t>
+          <t>0.0002036728923464626</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.065795612938224</t>
+          <t>0.0696132904526523</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.07482042953939759</t>
+          <t>0.09535589080595058</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.9130721947444821</t>
+          <t>0.988611689761863</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -3595,24 +3595,24 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ4" t="inlineStr">
         <is>
           <t>False</t>
@@ -3690,32 +3690,32 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1108436.0</t>
+          <t>1555506.0</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>312000.0</t>
+          <t>192000.0</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1033000.0</t>
+          <t>883000.0</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-721000.0</t>
+          <t>-691000.0</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>13273.0</t>
+          <t>14905.0</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>400709.0</t>
+          <t>879411.0</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -3800,17 +3800,17 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -3821,110 +3821,110 @@
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="CK4" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="CL4" t="n">
-        <v>-1.41</v>
+        <v>-1.42</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>211.7</t>
+          <t>211.4</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>212.95</t>
+          <t>212.35</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>214.72</t>
+          <t>214.45</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>219.34</t>
+          <t>218.73</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>224.42</t>
+          <t>224.21</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>226.1395833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>-0.001415094339622724</t>
+          <t>-0.001417099669343336</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>-0.003043071161048738</t>
+          <t>-0.002817562808170915</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>-0.001279069767441854</t>
+          <t>-0.001280707882174936</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>-0.002365141453652408</t>
+          <t>-0.002781070484179859</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>-0.0007235688642752702</t>
+          <t>-0.0009468905784386639</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>-0.0006536669796902705</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.80</t>
         </is>
       </c>
       <c r="DB4" t="n">
-        <v>-2.34</v>
+        <v>-2.38</v>
       </c>
       <c r="DC4" t="n">
-        <v>-2.19</v>
+        <v>-2.23</v>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>-153.39</t>
+          <t>-154.32</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
@@ -3943,48 +3943,48 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>869739959.7826705</t>
+          <t>1108834326.963768</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>242656285.0</t>
+          <t>329846967.0</t>
         </is>
       </c>
       <c r="DI4" t="n">
-        <v>401567743.4</v>
+        <v>404181891.4</v>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>402197533.1</t>
+          <t>374922599.4</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>360892111.8</t>
+          <t>330701942.7</t>
         </is>
       </c>
       <c r="DL4" t="n">
-        <v>499527332.66</v>
+        <v>492655844.94</v>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>636367710.4625</t>
+          <t>630795391.725</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>-2799714.512700467</t>
+          <t>-1548425.956954639</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>11251584.0961445</t>
+          <t>5333661.089675188</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>242656285.0</t>
+          <t>329846967.0</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="EI4" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="EK4" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>77.83</t>
         </is>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>221439</t>
         </is>
       </c>
       <c r="EM4" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="EP4" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="EQ4" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="ES4" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="ET4" t="inlineStr">
@@ -4154,42 +4154,42 @@
       </c>
       <c r="EX4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF4" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2981.945</t>
+          <t>1150.568</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.10931235303462698</t>
+          <t>-0.0015658716132489568</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>214.725</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>219.4009568337682</t>
+          <t>219.4095209832088</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>210.5990431662318</t>
+          <t>210.0404790167912</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.04093913333737826</t>
+          <t>0.04363274870842971</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.001509346336932449</t>
+          <t>-0.001279069767441854</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.0006322047883757786</t>
+          <t>3.903423927087424e-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.1194388933025705</t>
+          <t>0.06579561293835745</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.07482042953939759</t>
+          <t>0.09535589080595058</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.8440885667632837</t>
+          <t>0.9130721947443678</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -4581,24 +4581,24 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>False</t>
@@ -4676,32 +4676,32 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1108436.0</t>
+          <t>1555506.0</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>312000.0</t>
+          <t>192000.0</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1033000.0</t>
+          <t>883000.0</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-721000.0</t>
+          <t>-691000.0</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>13273.0</t>
+          <t>14905.0</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>400709.0</t>
+          <t>879411.0</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -4786,17 +4786,17 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -4807,307 +4807,307 @@
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="CK5" t="n">
-        <v>-0.71</v>
+        <v>-0.33</v>
       </c>
       <c r="CL5" t="n">
-        <v>-1.4</v>
+        <v>-1.41</v>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
+          <t>211.7</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>212.95</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>214.72</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>219.34</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>224.42</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>-0.001415094339622724</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>-0.003043071161048738</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>-0.001279069767441854</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>-0.002365141453652408</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>-0.0007235688642752702</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>-6.95</t>
+        </is>
+      </c>
+      <c r="DB5" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>-153.39</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>1108834326.963768</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>401567743.4</v>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>402197533.1</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>360892111.8</t>
+        </is>
+      </c>
+      <c r="DL5" t="n">
+        <v>499527332.66</v>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>636367710.4625</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>-2799714.510887335</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>11251584.09653378</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>242656285.0</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>-6.64</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>5.35</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>19.19</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>77.83</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>221439</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>213.6</t>
-        </is>
-      </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>215.0</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>219.86</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>224.58</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>226.2875</t>
-        </is>
-      </c>
-      <c r="CU5" t="inlineStr">
-        <is>
-          <t>-0.002352941176470558</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>-0.002102312543798224</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
-        <is>
-          <t>-0.001509346336932449</t>
-        </is>
-      </c>
-      <c r="CX5" t="inlineStr">
-        <is>
-          <t>-0.002631101433496541</t>
-        </is>
-      </c>
-      <c r="CY5" t="inlineStr">
-        <is>
-          <t>-0.0006396707086437914</t>
-        </is>
-      </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>-0.0006900168364107895</t>
-        </is>
-      </c>
-      <c r="DA5" t="inlineStr">
-        <is>
-          <t>-7.43</t>
-        </is>
-      </c>
-      <c r="DB5" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="DD5" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE5" t="inlineStr">
-        <is>
-          <t>-152.47</t>
-        </is>
-      </c>
-      <c r="DF5" t="inlineStr">
-        <is>
-          <t>2026/10/07</t>
-        </is>
-      </c>
-      <c r="DG5" t="inlineStr">
-        <is>
-          <t>869739959.7826705</t>
-        </is>
-      </c>
-      <c r="DH5" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DI5" t="n">
-        <v>446456989.4</v>
-      </c>
-      <c r="DJ5" t="inlineStr">
-        <is>
-          <t>402462830.4</t>
-        </is>
-      </c>
-      <c r="DK5" t="inlineStr">
-        <is>
-          <t>367213800.2333333</t>
-        </is>
-      </c>
-      <c r="DL5" t="n">
-        <v>514612178.2</v>
-      </c>
-      <c r="DM5" t="inlineStr">
-        <is>
-          <t>644200383.275</t>
-        </is>
-      </c>
-      <c r="DN5" t="inlineStr">
-        <is>
-          <t>-5354496.077945007</t>
-        </is>
-      </c>
-      <c r="DO5" t="inlineStr">
-        <is>
-          <t>28645776.31672496</t>
-        </is>
-      </c>
-      <c r="DP5" t="inlineStr">
-        <is>
-          <t>627997406.0</t>
-        </is>
-      </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR5" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS5" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT5" t="inlineStr">
-        <is>
-          <t>-6.86</t>
-        </is>
-      </c>
-      <c r="DU5" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV5" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW5" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ5" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>5.34</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK5" t="inlineStr">
-        <is>
-          <t>77.64</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
-        <is>
-          <t>221959</t>
-        </is>
-      </c>
-      <c r="EM5" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN5" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO5" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP5" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
-      <c r="EQ5" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ER5" t="inlineStr">
         <is>
           <t>210.0</t>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="ES5" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>211.0</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
@@ -5140,42 +5140,42 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF5" t="inlineStr">
@@ -5185,22 +5185,22 @@
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK5" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2207.66</t>
+          <t>2981.945</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5402,359 +5402,359 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>210.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.10931235303462698</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>空頭</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>TrendType : 空頭&lt;br&gt;TrendScore : 0&lt;br&gt;HH : False&lt;br&gt;HL : False&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>219.4009568337635</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>210.5990431662365</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.04093913333733463</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.0006322047883784432</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.1194388933028725</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.09535589080595058</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.8440885667630521</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>1555506.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>192000.0</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>883000.0</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>-691000.0</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>14905.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>879411.0</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.1244041204927823</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>215.325</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>219.2623381336896</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>211.3876618663104</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.03657111931907204</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.0002231618605739172</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.06116199241267872</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.07482042953939759</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0.7416038667766317</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>1108436.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>312000.0</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>1033000.0</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>-721000.0</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>13273.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>400709.0</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -5772,17 +5772,17 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -5793,17 +5793,17 @@
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -5812,283 +5812,283 @@
         </is>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="CL6" t="n">
-        <v>-1.31</v>
+        <v>-1.4</v>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>213.6</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>219.86</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>224.58</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>-0.002352941176470558</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>-0.002102312543798224</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>-0.001509346336932449</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>-0.002631101433496541</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>-0.0006396707086437914</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>-7.43</t>
+        </is>
+      </c>
+      <c r="DB6" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>-152.47</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>1108834326.963768</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DI6" t="n">
+        <v>446456989.4</v>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>402462830.4</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>367213800.2333333</t>
+        </is>
+      </c>
+      <c r="DL6" t="n">
+        <v>514612178.2</v>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>644200383.275</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>-5354496.075872992</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>28645776.31716985</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>627997406.0</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>226.0</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>-6.86</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>統一超</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>貿易百貨</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>0.5136495342743107</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>4.882515139066092</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>4.66483663592919</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>5.34</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>88.66</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>19.19</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>34.59%</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>77.83</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>221439</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>統一超-貿易百貨-上市</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>214.05</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>215.32</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>220.44</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>224.72</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>226.44375</t>
-        </is>
-      </c>
-      <c r="CU6" t="inlineStr">
-        <is>
-          <t>-0.00140977443609025</t>
-        </is>
-      </c>
-      <c r="CV6" t="inlineStr">
-        <is>
-          <t>-0.001399580125962085</t>
-        </is>
-      </c>
-      <c r="CW6" t="inlineStr">
-        <is>
-          <t>-0.0008120649651972567</t>
-        </is>
-      </c>
-      <c r="CX6" t="inlineStr">
-        <is>
-          <t>-0.00275955666138894</t>
-        </is>
-      </c>
-      <c r="CY6" t="inlineStr">
-        <is>
-          <t>-0.001083483817196806</t>
-        </is>
-      </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>-0.0006527895259461625</t>
-        </is>
-      </c>
-      <c r="DA6" t="inlineStr">
-        <is>
-          <t>-3.62</t>
-        </is>
-      </c>
-      <c r="DB6" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>-2.11</v>
-      </c>
-      <c r="DD6" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="DE6" t="inlineStr">
-        <is>
-          <t>-151.49</t>
-        </is>
-      </c>
-      <c r="DF6" t="inlineStr">
-        <is>
-          <t>2026/10/07</t>
-        </is>
-      </c>
-      <c r="DG6" t="inlineStr">
-        <is>
-          <t>869739959.7826705</t>
-        </is>
-      </c>
-      <c r="DH6" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DI6" t="n">
-        <v>418130651</v>
-      </c>
-      <c r="DJ6" t="inlineStr">
-        <is>
-          <t>371868657.7</t>
-        </is>
-      </c>
-      <c r="DK6" t="inlineStr">
-        <is>
-          <t>365219125.0</t>
-        </is>
-      </c>
-      <c r="DL6" t="n">
-        <v>527411299.66</v>
-      </c>
-      <c r="DM6" t="inlineStr">
-        <is>
-          <t>653166606.5875</t>
-        </is>
-      </c>
-      <c r="DN6" t="inlineStr">
-        <is>
-          <t>-11536363.78606682</t>
-        </is>
-      </c>
-      <c r="DO6" t="inlineStr">
-        <is>
-          <t>11185010.22767115</t>
-        </is>
-      </c>
-      <c r="DP6" t="inlineStr">
-        <is>
-          <t>467278976.0</t>
-        </is>
-      </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DR6" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="DS6" t="inlineStr">
-        <is>
-          <t>2026/06/25</t>
-        </is>
-      </c>
-      <c r="DT6" t="inlineStr">
-        <is>
-          <t>-5.97</t>
-        </is>
-      </c>
-      <c r="DU6" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DV6" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-      <c r="DW6" t="inlineStr">
-        <is>
-          <t>貿易百貨</t>
-        </is>
-      </c>
-      <c r="DX6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="DY6" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="DZ6" t="inlineStr">
-        <is>
-          <t>0.5136495342743107</t>
-        </is>
-      </c>
-      <c r="EA6" t="inlineStr">
-        <is>
-          <t>4.882515139066092</t>
-        </is>
-      </c>
-      <c r="EB6" t="inlineStr">
-        <is>
-          <t>4.66483663592919</t>
-        </is>
-      </c>
-      <c r="EC6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="EE6" t="inlineStr">
-        <is>
-          <t>5.39</t>
-        </is>
-      </c>
-      <c r="EF6" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
-        <is>
-          <t>88.66</t>
-        </is>
-      </c>
-      <c r="EH6" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr">
-        <is>
-          <t>34.59%</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>4.17%</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr">
-        <is>
-          <t>77.64</t>
-        </is>
-      </c>
-      <c r="EL6" t="inlineStr">
-        <is>
-          <t>221959</t>
-        </is>
-      </c>
-      <c r="EM6" t="inlineStr">
-        <is>
-          <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
-        </is>
-      </c>
-      <c r="EN6" t="inlineStr">
-        <is>
-          <t>統一超-貿易百貨-上市</t>
-        </is>
-      </c>
-      <c r="EO6" t="inlineStr">
-        <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="EP6" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
       <c r="EQ6" t="inlineStr">
         <is>
           <t>212.5</t>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="ER6" t="inlineStr">
         <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ES6" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET6" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -6126,42 +6126,42 @@
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="FA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF6" t="inlineStr">
@@ -6171,22 +6171,22 @@
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK6" t="inlineStr">
@@ -6373,374 +6373,374 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2207.66</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>212.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1661.585</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.1244041204927823</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>215.325</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>219.2623381336843</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>211.3876618663157</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.0365711193190232</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-0.0008120649651972567</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.0002231618605752494</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.06116199241285347</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.09535589080595058</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.7416038667762083</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>1555506.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>192000.0</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>883000.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>-691000.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>14905.0</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>879411.0</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.04757601939330377</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>215.5</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>219.2134180594527</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>211.7865819405473</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.03446327665385303</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>-0.0009272137227630539</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0.0002666812745690805</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0.07580111770054776</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.07482042953939759</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0.6844365996151905</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>1108436.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>312000.0</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1033000.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>-721000.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>13273.0</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>400709.0</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -6758,17 +6758,17 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>8.19</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -6779,12 +6779,12 @@
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -6794,95 +6794,95 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="CK7" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-1.25</v>
+        <v>-1.31</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>212.8</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>214.35</t>
+          <t>214.05</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.32</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>221.05</t>
+          <t>220.44</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>224.97</t>
+          <t>224.72</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>226.5916666666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>-0.002344116268166885</t>
+          <t>-0.00140977443609025</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>-0.001862630966239842</t>
+          <t>-0.001399580125962085</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>-0.0009272137227630539</t>
+          <t>-0.0008120649651972567</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>-0.002796950421798061</t>
+          <t>-0.00275955666138894</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>-0.00185791137485436</t>
+          <t>-0.001083483817196806</t>
         </is>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>-0.000652363669775391</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="DB7" t="n">
-        <v>-2.2</v>
+        <v>-2.19</v>
       </c>
       <c r="DC7" t="n">
-        <v>-2.09</v>
+        <v>-2.11</v>
       </c>
       <c r="DD7" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="DE7" t="inlineStr">
         <is>
-          <t>-151.02</t>
+          <t>-151.49</t>
         </is>
       </c>
       <c r="DF7" t="inlineStr">
@@ -6901,48 +6901,48 @@
       </c>
       <c r="DG7" t="inlineStr">
         <is>
-          <t>869739959.7826705</t>
+          <t>1108834326.963768</t>
         </is>
       </c>
       <c r="DH7" t="inlineStr">
         <is>
-          <t>353129823.0</t>
+          <t>467278976.0</t>
         </is>
       </c>
       <c r="DI7" t="n">
-        <v>366032679.6</v>
+        <v>418130651</v>
       </c>
       <c r="DJ7" t="inlineStr">
         <is>
-          <t>349409181.6</t>
+          <t>371868657.7</t>
         </is>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
-          <t>361747717.0333334</t>
+          <t>365219125.0</t>
         </is>
       </c>
       <c r="DL7" t="n">
-        <v>541988911.52</v>
+        <v>527411299.66</v>
       </c>
       <c r="DM7" t="inlineStr">
         <is>
-          <t>663738938.0125</t>
+          <t>653166606.5875</t>
         </is>
       </c>
       <c r="DN7" t="inlineStr">
         <is>
-          <t>-15667522.69765554</t>
+          <t>-11536363.78369896</t>
         </is>
       </c>
       <c r="DO7" t="inlineStr">
         <is>
-          <t>3061425.806606054</t>
+          <t>11185010.22817957</t>
         </is>
       </c>
       <c r="DP7" t="inlineStr">
         <is>
-          <t>353129823.0</t>
+          <t>467278976.0</t>
         </is>
       </c>
       <c r="DQ7" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="EI7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="EK7" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>77.83</t>
         </is>
       </c>
       <c r="EL7" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>221439</t>
         </is>
       </c>
       <c r="EM7" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="ES7" t="inlineStr">
@@ -7112,42 +7112,42 @@
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF7" t="inlineStr">
@@ -7157,22 +7157,22 @@
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK7" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1493.082</t>
+          <t>1661.585</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.02818205226401916</t>
+          <t>0.04757601939330377</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -7454,47 +7454,47 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>219.1549735317831</t>
+          <t>219.2134180594471</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>212.2450264682169</t>
+          <t>211.7865819405529</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.03203498870452557</t>
+          <t>0.03446327665380133</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0015044555028354</t>
+          <t>-0.0009272137227630539</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0003340450614971457</t>
+          <t>0.0002666812745708569</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.08022388064267094</t>
+          <t>0.07580111770079268</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.07482042953939759</t>
+          <t>0.09535589080595058</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.6227152067319971</t>
+          <t>0.6844365996146634</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -7539,142 +7539,142 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>1555506.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>192000.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>883000.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-691000.0</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>14905.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>879411.0</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>1108436.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>312000.0</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1033000.0</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-721000.0</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>13273.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>400709.0</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -7744,17 +7744,17 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>8.19</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -7765,110 +7765,110 @@
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CK8" t="n">
-        <v>-0.61</v>
+        <v>-0.14</v>
       </c>
       <c r="CL8" t="n">
-        <v>-1.11</v>
+        <v>-1.25</v>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>213.3</t>
+          <t>212.8</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>214.75</t>
+          <t>214.35</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>215.7</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>221.67</t>
+          <t>221.05</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>225.39</t>
+          <t>224.97</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>226.7395833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>-0.004201680672268782</t>
+          <t>-0.002344116268166885</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>-0.002091078066914442</t>
+          <t>-0.001862630966239842</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>-0.0015044555028354</t>
+          <t>-0.0009272137227630539</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>-0.002789149309460615</t>
+          <t>-0.002796950421798061</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>-0.001495182190718869</t>
+          <t>-0.00185791137485436</t>
         </is>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>-0.000661114528909934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="DB8" t="n">
-        <v>-2.19</v>
+        <v>-2.2</v>
       </c>
       <c r="DC8" t="n">
-        <v>-2.06</v>
+        <v>-2.09</v>
       </c>
       <c r="DD8" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="DE8" t="inlineStr">
         <is>
-          <t>-150.35</t>
+          <t>-151.02</t>
         </is>
       </c>
       <c r="DF8" t="inlineStr">
@@ -7887,48 +7887,48 @@
       </c>
       <c r="DG8" t="inlineStr">
         <is>
-          <t>869739959.7826705</t>
+          <t>1108834326.963768</t>
         </is>
       </c>
       <c r="DH8" t="inlineStr">
         <is>
-          <t>316776227.0</t>
+          <t>353129823.0</t>
         </is>
       </c>
       <c r="DI8" t="n">
-        <v>345663307.4</v>
+        <v>366032679.6</v>
       </c>
       <c r="DJ8" t="inlineStr">
         <is>
-          <t>336188816.6</t>
+          <t>349409181.6</t>
         </is>
       </c>
       <c r="DK8" t="inlineStr">
         <is>
-          <t>367617217.2</t>
+          <t>361747717.0333334</t>
         </is>
       </c>
       <c r="DL8" t="n">
-        <v>561834701.02</v>
+        <v>541988911.52</v>
       </c>
       <c r="DM8" t="inlineStr">
         <is>
-          <t>700692145.4125</t>
+          <t>663738938.0125</t>
         </is>
       </c>
       <c r="DN8" t="inlineStr">
         <is>
-          <t>-19072786.06206674</t>
+          <t>-15667522.6949496</t>
         </is>
       </c>
       <c r="DO8" t="inlineStr">
         <is>
-          <t>3577234.96199137</t>
+          <t>3061425.80718708</t>
         </is>
       </c>
       <c r="DP8" t="inlineStr">
         <is>
-          <t>316776227.0</t>
+          <t>353129823.0</t>
         </is>
       </c>
       <c r="DQ8" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="DT8" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU8" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="EK8" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>77.83</t>
         </is>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>221439</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
@@ -8058,22 +8058,22 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES8" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
@@ -8098,42 +8098,42 @@
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF8" t="inlineStr">
@@ -8143,22 +8143,22 @@
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK8" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2196.33</t>
+          <t>1493.082</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8360,359 +8360,359 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>212.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.02818205226401916</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>弱勢整理</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>215.7</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>219.1549735317771</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>212.2450264682229</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.03203498870447023</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-0.0015044555028354</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-0.0003340450614949253</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.08022388064298025</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.09535589080595058</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.622715206731353</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2026-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2026-07-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>1555506.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>192000.0</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>883000.0</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-691000.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>14905.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>879411.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>217.0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>2026/05/25</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.22693734286617706</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>弱勢整理</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>TrendType : 弱勢整理&lt;br&gt;TrendScore : 30&lt;br&gt;HH : False&lt;br&gt;HL : True&lt;br&gt;MA : False&lt;br&gt;VOL : False</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>216.025</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>219.228205631215</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>212.821794368785</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.02965587900673572</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>-0.001848215317084456</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.002463797900746689</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.04052320117702157</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.07482042953939759</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0.563943123073434</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2026-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2026-07-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>盤整</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>1108436.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>312000.0</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1033000.0</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>-721000.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>13273.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>400709.0</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>217.0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>2026/05/25</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>2026/09/24</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>2026/09/24</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
           <t>2026/07/23</t>
@@ -8730,17 +8730,17 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -8751,12 +8751,12 @@
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -8770,91 +8770,91 @@
         </is>
       </c>
       <c r="CK9" t="n">
-        <v>-0.79</v>
+        <v>-0.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0.84</v>
+        <v>-1.11</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>214.2</t>
+          <t>213.3</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>215.2</t>
+          <t>214.75</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>216.02</t>
+          <t>215.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>222.29</t>
+          <t>221.67</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>225.72</t>
+          <t>225.39</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>226.8895833333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>-0.004646840148698872</t>
+          <t>-0.004201680672268782</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>-0.002780352177942591</t>
+          <t>-0.002091078066914442</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>-0.001848215317084456</t>
+          <t>-0.0015044555028354</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>-0.002960305001121322</t>
+          <t>-0.002789149309460615</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>-0.001133943634704204</t>
+          <t>-0.001495182190718869</t>
         </is>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>-0.0006973564684401579</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="DB9" t="n">
-        <v>-2.09</v>
+        <v>-2.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>-2.03</v>
+        <v>-2.06</v>
       </c>
       <c r="DD9" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="DE9" t="inlineStr">
         <is>
-          <t>-149.59</t>
+          <t>-150.35</t>
         </is>
       </c>
       <c r="DF9" t="inlineStr">
@@ -8873,48 +8873,48 @@
       </c>
       <c r="DG9" t="inlineStr">
         <is>
-          <t>869739959.7826705</t>
+          <t>1108834326.963768</t>
         </is>
       </c>
       <c r="DH9" t="inlineStr">
         <is>
-          <t>467102515.0</t>
+          <t>316776227.0</t>
         </is>
       </c>
       <c r="DI9" t="n">
-        <v>402827322.8</v>
+        <v>345663307.4</v>
       </c>
       <c r="DJ9" t="inlineStr">
         <is>
-          <t>328319392.3</t>
+          <t>336188816.6</t>
         </is>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
-          <t>376703314.4666666</t>
+          <t>367617217.2</t>
         </is>
       </c>
       <c r="DL9" t="n">
-        <v>582922481.98</v>
+        <v>561834701.02</v>
       </c>
       <c r="DM9" t="inlineStr">
         <is>
-          <t>734035263.775</t>
+          <t>700692145.4125</t>
         </is>
       </c>
       <c r="DN9" t="inlineStr">
         <is>
-          <t>-23190971.70280458</t>
+          <t>-19072786.05897446</t>
         </is>
       </c>
       <c r="DO9" t="inlineStr">
         <is>
-          <t>8081374.935327888</t>
+          <t>3577234.962655425</t>
         </is>
       </c>
       <c r="DP9" t="inlineStr">
         <is>
-          <t>467102515.0</t>
+          <t>316776227.0</t>
         </is>
       </c>
       <c r="DQ9" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="DT9" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="DU9" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="EC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED9" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="EK9" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>77.83</t>
         </is>
       </c>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>221439</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
@@ -9049,19 +9049,19 @@
       </c>
       <c r="EQ9" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="ER9" t="inlineStr">
         <is>
+          <t>211.5</t>
+        </is>
+      </c>
+      <c r="ES9" t="inlineStr">
+        <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ES9" t="inlineStr">
-        <is>
-          <t>212.5</t>
-        </is>
-      </c>
       <c r="ET9" t="inlineStr">
         <is>
           <t>206.5</t>
@@ -9084,42 +9084,42 @@
       </c>
       <c r="EX9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF9" t="inlineStr">
@@ -9129,22 +9129,22 @@
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK9" t="inlineStr">
@@ -9321,7 +9321,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9331,12 +9331,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2277.177</t>
+          <t>2196.33</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.15575456569198345</t>
+          <t>0.22693734286617706</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9426,47 +9426,47 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>216.425</t>
+          <t>216.025</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>219.769673691905</t>
+          <t>219.2282056312086</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>213.0803263080951</t>
+          <t>212.8217943687914</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.03090838574014041</t>
+          <t>0.02965587900667599</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.0023049441051054</t>
+          <t>-0.001848215317084456</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.005655295743209665</t>
+          <t>-0.002463797900748133</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.1812639188507745</t>
+          <t>-0.04052320117718478</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.07482042953939759</t>
+          <t>0.09535589080595058</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.5727216399708794</t>
+          <t>0.5639431230726679</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -9511,142 +9511,142 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>盤整</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>弱勢</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>1555506.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>192000.0</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>883000.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>-691000.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>14905.0</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>879411.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>弱勢</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>83.3</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>1108436.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>312000.0</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>1033000.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>-721000.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>13273.0</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>400709.0</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -9737,12 +9737,12 @@
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>50</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -9756,91 +9756,91 @@
         </is>
       </c>
       <c r="CK10" t="n">
-        <v>-1.02</v>
+        <v>-0.79</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0.57</v>
+        <v>-0.84</v>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
+          <t>214.2</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
           <t>215.2</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
-        <is>
-          <t>215.8</t>
-        </is>
-      </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>216.42</t>
+          <t>216.02</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>222.95</t>
+          <t>222.29</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>225.98</t>
+          <t>225.72</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>227.0479166666667</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>-0.001855287569573316</t>
+          <t>-0.004646840148698872</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>-0.002080924855491273</t>
+          <t>-0.002780352177942591</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>-0.0023049441051054</t>
+          <t>-0.001848215317084456</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>-0.002817783343769698</t>
+          <t>-0.002960305001121322</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>-0.0008014149118443781</t>
+          <t>-0.001133943634704204</t>
         </is>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>-0.0006418897233454457</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="DB10" t="n">
-        <v>-1.98</v>
+        <v>-2.09</v>
       </c>
       <c r="DC10" t="n">
-        <v>-2.02</v>
+        <v>-2.03</v>
       </c>
       <c r="DD10" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="DE10" t="inlineStr">
         <is>
-          <t>-149.26</t>
+          <t>-149.59</t>
         </is>
       </c>
       <c r="DF10" t="inlineStr">
@@ -9859,48 +9859,48 @@
       </c>
       <c r="DG10" t="inlineStr">
         <is>
-          <t>869739959.7826705</t>
+          <t>1108834326.963768</t>
         </is>
       </c>
       <c r="DH10" t="inlineStr">
         <is>
-          <t>486365714.0</t>
+          <t>467102515.0</t>
         </is>
       </c>
       <c r="DI10" t="n">
-        <v>358468671.4</v>
+        <v>402827322.8</v>
       </c>
       <c r="DJ10" t="inlineStr">
         <is>
-          <t>310159857.5</t>
+          <t>328319392.3</t>
         </is>
       </c>
       <c r="DK10" t="inlineStr">
         <is>
-          <t>389696834.5333334</t>
+          <t>376703314.4666666</t>
         </is>
       </c>
       <c r="DL10" t="n">
-        <v>598546724.48</v>
+        <v>582922481.98</v>
       </c>
       <c r="DM10" t="inlineStr">
         <is>
-          <t>767533169.1875</t>
+          <t>734035263.775</t>
         </is>
       </c>
       <c r="DN10" t="inlineStr">
         <is>
-          <t>-28876852.90973775</t>
+          <t>-23190971.6992708</t>
         </is>
       </c>
       <c r="DO10" t="inlineStr">
         <is>
-          <t>-1879147.921881616</t>
+          <t>8081374.936086774</t>
         </is>
       </c>
       <c r="DP10" t="inlineStr">
         <is>
-          <t>486365714.0</t>
+          <t>467102515.0</t>
         </is>
       </c>
       <c r="DQ10" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="EC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="ED10" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="EE10" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="EF10" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EG10" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>19.23</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="EI10" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="EK10" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>77.83</t>
         </is>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>221439</t>
         </is>
       </c>
       <c r="EM10" t="inlineStr">
@@ -10030,22 +10030,22 @@
       </c>
       <c r="EP10" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="EQ10" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="ER10" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="ES10" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="ET10" t="inlineStr">
@@ -10070,42 +10070,42 @@
       </c>
       <c r="EX10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="EY10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="EZ10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="FA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FC10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FD10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FE10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FF10" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FI10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FJ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FK10" t="inlineStr">

--- a/Result/checksun_type/零售.xlsx
+++ b/Result/checksun_type/零售.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR10"/>
+  <dimension ref="A1:GS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,610 +821,615 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>voc_cross_d</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>MA_5</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>MA_10</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>MA_20</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>MA_50</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>MA_80</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>MA_240</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>MA_5_斜率</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>MA_10_斜率</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>MA_20_斜率</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>MA_50_斜率</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>MA_80_斜率</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>MA_240_斜率</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_5</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_10</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_30</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_50</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_80</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>成交金額_補值</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>最小收盤價</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>多頭排列_前5日次數</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>下跌帶量_前15日次數</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>MA_break_前15日次數</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>抄底訊號_前15日次數</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>黃金交叉_前15日次數</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>量起點_前15日次數</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>價過5日_前15日次數</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>量短5長30比</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前10日次數</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前5日次數</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前2日次數</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前1日次數</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>季別</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>營業收入</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>營業成本</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>營業毛利</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>營業利益</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>營益率</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>業外收支</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>稅前淨利</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>稅後淨利</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>EPS(元)</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>EPS_前8季全為正</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>去年同季比較</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>EPS_MA_8</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>GM_MA_8</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>EPS_維持</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>毛利率_維持</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>EPS_創新高</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>毛利率_創新高</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>財報健康</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>財報強勢</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ_%</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ_%</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY_%</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY_%</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>EPS_成長</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY成長</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>毛利率成長</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>毛利率YoY成長</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>財報動能強</t>
         </is>
@@ -1823,383 +1828,383 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>9.44</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>61.11</t>
         </is>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>0.61</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>-1.16</v>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>-1.63</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>-2.72</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>211.7</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>212.1</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>214.18</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>217.72</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>223.8</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
           <t>0.0004725897920605515</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>-0.0004712535344014723</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>-0.0009329446064139102</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>-0.002245543283992513</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>-0.0009486077785836322</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
           <t>8.87</t>
         </is>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>-1.97</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>-2.16</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>-152.73</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>406750587.0</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DJ2" t="n">
         <v>403026237</v>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>410578444.0</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>329080732.6</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="DM2" t="n">
         <v>480983763.3</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>626861142.9625</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>984214.4537600467</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>7756398.536886513</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>406750587.0</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>-5.75</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>5.40</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="EQ2" t="inlineStr">
+      <c r="ER2" t="inlineStr">
         <is>
           <t>213.5</t>
         </is>
       </c>
-      <c r="ER2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>211.5</t>
         </is>
       </c>
-      <c r="ES2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>213.0</t>
         </is>
       </c>
-      <c r="ET2" t="inlineStr">
+      <c r="EU2" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU2" t="inlineStr">
+      <c r="EV2" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV2" t="inlineStr">
+      <c r="EW2" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX2" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2207,14 +2212,14 @@
       </c>
       <c r="FC2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2222,12 +2227,12 @@
       </c>
       <c r="FF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH2" t="inlineStr">
@@ -2247,170 +2252,175 @@
       </c>
       <c r="FK2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL2" t="inlineStr">
+      <c r="FM2" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM2" t="inlineStr">
+      <c r="FN2" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN2" t="inlineStr">
+      <c r="FO2" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FP2" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FQ2" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT2" t="inlineStr">
+      <c r="FU2" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU2" t="inlineStr">
+      <c r="FV2" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV2" t="inlineStr">
+      <c r="FW2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW2" t="inlineStr">
+      <c r="FX2" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX2" t="inlineStr">
+      <c r="FY2" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ2" t="inlineStr">
+      <c r="GA2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA2" t="inlineStr">
+      <c r="GB2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB2" t="inlineStr">
+      <c r="GC2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE2" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG2" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG2" t="inlineStr">
+      <c r="GH2" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH2" t="inlineStr">
+      <c r="GI2" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI2" t="inlineStr">
+      <c r="GJ2" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ2" t="inlineStr">
+      <c r="GK2" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK2" t="inlineStr">
+      <c r="GL2" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL2" t="inlineStr">
+      <c r="GM2" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM2" t="inlineStr">
+      <c r="GN2" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN2" t="inlineStr">
+      <c r="GO2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO2" t="inlineStr">
+      <c r="GP2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP2" t="inlineStr">
+      <c r="GQ2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ2" t="inlineStr">
+      <c r="GR2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR2" t="inlineStr">
+      <c r="GS2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -2809,383 +2819,383 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>9.46</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>37.04</t>
         </is>
       </c>
-      <c r="CK3" t="n">
+      <c r="CL3" t="n">
         <v>0.9</v>
       </c>
-      <c r="CL3" t="n">
+      <c r="CM3" t="n">
         <v>-1.29</v>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>-1.76</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>-2.59</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>211.6</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>212.2</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>214.38</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>218.21</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>224.01</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
           <t>0.0009460737937558861</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>-0.0007063809748057981</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>-0.000349731872231196</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>-0.002377360215791047</t>
         </is>
       </c>
-      <c r="CY3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>-0.0008641596744070057</t>
         </is>
       </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="DB3" t="n">
+      <c r="DC3" t="n">
         <v>-2.14</v>
       </c>
-      <c r="DC3" t="n">
+      <c r="DD3" t="n">
         <v>-2.21</v>
       </c>
-      <c r="DD3" t="inlineStr">
+      <c r="DE3" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE3" t="inlineStr">
+      <c r="DF3" t="inlineStr">
         <is>
           <t>-153.90</t>
         </is>
       </c>
-      <c r="DF3" t="inlineStr">
+      <c r="DG3" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG3" t="inlineStr">
+      <c r="DH3" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH3" t="inlineStr">
+      <c r="DI3" t="inlineStr">
         <is>
           <t>407879940.0</t>
         </is>
       </c>
-      <c r="DI3" t="n">
+      <c r="DJ3" t="n">
         <v>415131914.8</v>
       </c>
-      <c r="DJ3" t="inlineStr">
+      <c r="DK3" t="inlineStr">
         <is>
           <t>390582297.2</t>
         </is>
       </c>
-      <c r="DK3" t="inlineStr">
+      <c r="DL3" t="inlineStr">
         <is>
           <t>325795920.4</t>
         </is>
       </c>
-      <c r="DL3" t="n">
+      <c r="DM3" t="n">
         <v>484522306.52</v>
       </c>
-      <c r="DM3" t="inlineStr">
+      <c r="DN3" t="inlineStr">
         <is>
           <t>626541939.95</t>
         </is>
       </c>
-      <c r="DN3" t="inlineStr">
+      <c r="DO3" t="inlineStr">
         <is>
           <t>-247091.7431720381</t>
         </is>
       </c>
-      <c r="DO3" t="inlineStr">
+      <c r="DP3" t="inlineStr">
         <is>
           <t>6910246.432632267</t>
         </is>
       </c>
-      <c r="DP3" t="inlineStr">
+      <c r="DQ3" t="inlineStr">
         <is>
           <t>407879940.0</t>
         </is>
       </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS3" t="inlineStr">
+      <c r="DT3" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT3" t="inlineStr">
+      <c r="DU3" t="inlineStr">
         <is>
           <t>-5.53</t>
         </is>
       </c>
-      <c r="DU3" t="inlineStr">
+      <c r="DV3" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV3" t="inlineStr">
+      <c r="DW3" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW3" t="inlineStr">
+      <c r="DX3" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX3" t="inlineStr">
+      <c r="DY3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY3" t="inlineStr">
+      <c r="DZ3" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ3" t="inlineStr">
+      <c r="EA3" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA3" t="inlineStr">
+      <c r="EB3" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB3" t="inlineStr">
+      <c r="EC3" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC3" t="inlineStr">
+      <c r="ED3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
+      <c r="EE3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE3" t="inlineStr">
+      <c r="EF3" t="inlineStr">
         <is>
           <t>5.42</t>
         </is>
       </c>
-      <c r="EF3" t="inlineStr">
+      <c r="EG3" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG3" t="inlineStr">
+      <c r="EH3" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH3" t="inlineStr">
+      <c r="EI3" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI3" t="inlineStr">
+      <c r="EJ3" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ3" t="inlineStr">
+      <c r="EK3" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK3" t="inlineStr">
+      <c r="EL3" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL3" t="inlineStr">
+      <c r="EM3" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM3" t="inlineStr">
+      <c r="EN3" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN3" t="inlineStr">
+      <c r="EO3" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO3" t="inlineStr">
+      <c r="EP3" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP3" t="inlineStr">
+      <c r="EQ3" t="inlineStr">
         <is>
           <t>211.0</t>
         </is>
       </c>
-      <c r="EQ3" t="inlineStr">
+      <c r="ER3" t="inlineStr">
         <is>
           <t>214.0</t>
         </is>
       </c>
-      <c r="ER3" t="inlineStr">
+      <c r="ES3" t="inlineStr">
         <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ES3" t="inlineStr">
+      <c r="ET3" t="inlineStr">
         <is>
           <t>213.5</t>
         </is>
       </c>
-      <c r="ET3" t="inlineStr">
+      <c r="EU3" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU3" t="inlineStr">
+      <c r="EV3" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV3" t="inlineStr">
+      <c r="EW3" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="FA3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3193,14 +3203,14 @@
       </c>
       <c r="FC3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FD3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="FD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FE3" t="inlineStr">
         <is>
           <t>0</t>
@@ -3208,12 +3218,12 @@
       </c>
       <c r="FF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
@@ -3233,170 +3243,175 @@
       </c>
       <c r="FK3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL3" t="inlineStr">
+      <c r="FM3" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM3" t="inlineStr">
+      <c r="FN3" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN3" t="inlineStr">
+      <c r="FO3" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO3" t="inlineStr">
+      <c r="FP3" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP3" t="inlineStr">
+      <c r="FQ3" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ3" t="inlineStr">
+      <c r="FR3" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR3" t="inlineStr">
+      <c r="FS3" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS3" t="inlineStr">
+      <c r="FT3" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT3" t="inlineStr">
+      <c r="FU3" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU3" t="inlineStr">
+      <c r="FV3" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV3" t="inlineStr">
+      <c r="FW3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW3" t="inlineStr">
+      <c r="FX3" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX3" t="inlineStr">
+      <c r="FY3" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY3" t="inlineStr">
+      <c r="FZ3" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ3" t="inlineStr">
+      <c r="GA3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA3" t="inlineStr">
+      <c r="GB3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB3" t="inlineStr">
+      <c r="GC3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE3" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG3" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG3" t="inlineStr">
+      <c r="GH3" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH3" t="inlineStr">
+      <c r="GI3" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI3" t="inlineStr">
+      <c r="GJ3" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ3" t="inlineStr">
+      <c r="GK3" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK3" t="inlineStr">
+      <c r="GL3" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL3" t="inlineStr">
+      <c r="GM3" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM3" t="inlineStr">
+      <c r="GN3" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN3" t="inlineStr">
+      <c r="GO3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO3" t="inlineStr">
+      <c r="GP3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP3" t="inlineStr">
+      <c r="GQ3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ3" t="inlineStr">
+      <c r="GR3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR3" t="inlineStr">
+      <c r="GS3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -3795,383 +3810,383 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>7.72</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>-0.47</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CJ4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="CK4" t="n">
+      <c r="CL4" t="n">
         <v>-0.43</v>
       </c>
-      <c r="CL4" t="n">
+      <c r="CM4" t="n">
         <v>-1.42</v>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>-1.96</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>-2.44</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>211.4</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>212.35</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>214.45</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>218.73</t>
         </is>
       </c>
-      <c r="CS4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>224.21</t>
         </is>
       </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
           <t>-0.001417099669343336</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>-0.002817562808170915</t>
         </is>
       </c>
-      <c r="CW4" t="inlineStr">
+      <c r="CX4" t="inlineStr">
         <is>
           <t>-0.001280707882174936</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
+      <c r="CY4" t="inlineStr">
         <is>
           <t>-0.002781070484179859</t>
         </is>
       </c>
-      <c r="CY4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>-0.0009468905784386639</t>
         </is>
       </c>
-      <c r="CZ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
           <t>-6.80</t>
         </is>
       </c>
-      <c r="DB4" t="n">
+      <c r="DC4" t="n">
         <v>-2.38</v>
       </c>
-      <c r="DC4" t="n">
+      <c r="DD4" t="n">
         <v>-2.23</v>
       </c>
-      <c r="DD4" t="inlineStr">
+      <c r="DE4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE4" t="inlineStr">
+      <c r="DF4" t="inlineStr">
         <is>
           <t>-154.32</t>
         </is>
       </c>
-      <c r="DF4" t="inlineStr">
+      <c r="DG4" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG4" t="inlineStr">
+      <c r="DH4" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH4" t="inlineStr">
+      <c r="DI4" t="inlineStr">
         <is>
           <t>329846967.0</t>
         </is>
       </c>
-      <c r="DI4" t="n">
+      <c r="DJ4" t="n">
         <v>404181891.4</v>
       </c>
-      <c r="DJ4" t="inlineStr">
+      <c r="DK4" t="inlineStr">
         <is>
           <t>374922599.4</t>
         </is>
       </c>
-      <c r="DK4" t="inlineStr">
+      <c r="DL4" t="inlineStr">
         <is>
           <t>330701942.7</t>
         </is>
       </c>
-      <c r="DL4" t="n">
+      <c r="DM4" t="n">
         <v>492655844.94</v>
       </c>
-      <c r="DM4" t="inlineStr">
+      <c r="DN4" t="inlineStr">
         <is>
           <t>630795391.725</t>
         </is>
       </c>
-      <c r="DN4" t="inlineStr">
+      <c r="DO4" t="inlineStr">
         <is>
           <t>-1548425.956954639</t>
         </is>
       </c>
-      <c r="DO4" t="inlineStr">
+      <c r="DP4" t="inlineStr">
         <is>
           <t>5333661.089675188</t>
         </is>
       </c>
-      <c r="DP4" t="inlineStr">
+      <c r="DQ4" t="inlineStr">
         <is>
           <t>329846967.0</t>
         </is>
       </c>
-      <c r="DQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS4" t="inlineStr">
+      <c r="DT4" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT4" t="inlineStr">
+      <c r="DU4" t="inlineStr">
         <is>
           <t>-6.86</t>
         </is>
       </c>
-      <c r="DU4" t="inlineStr">
+      <c r="DV4" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV4" t="inlineStr">
+      <c r="DW4" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW4" t="inlineStr">
+      <c r="DX4" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX4" t="inlineStr">
+      <c r="DY4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY4" t="inlineStr">
+      <c r="DZ4" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ4" t="inlineStr">
+      <c r="EA4" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA4" t="inlineStr">
+      <c r="EB4" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB4" t="inlineStr">
+      <c r="EC4" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="ED4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
+      <c r="EE4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE4" t="inlineStr">
+      <c r="EF4" t="inlineStr">
         <is>
           <t>5.34</t>
         </is>
       </c>
-      <c r="EF4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG4" t="inlineStr">
+      <c r="EH4" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH4" t="inlineStr">
+      <c r="EI4" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI4" t="inlineStr">
+      <c r="EJ4" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ4" t="inlineStr">
+      <c r="EK4" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK4" t="inlineStr">
+      <c r="EL4" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL4" t="inlineStr">
+      <c r="EM4" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM4" t="inlineStr">
+      <c r="EN4" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN4" t="inlineStr">
+      <c r="EO4" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO4" t="inlineStr">
+      <c r="EP4" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP4" t="inlineStr">
+      <c r="EQ4" t="inlineStr">
         <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="EQ4" t="inlineStr">
+      <c r="ER4" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ER4" t="inlineStr">
+      <c r="ES4" t="inlineStr">
         <is>
           <t>210.0</t>
         </is>
       </c>
-      <c r="ES4" t="inlineStr">
+      <c r="ET4" t="inlineStr">
         <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ET4" t="inlineStr">
+      <c r="EU4" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU4" t="inlineStr">
+      <c r="EV4" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV4" t="inlineStr">
+      <c r="EW4" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX4" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="FA4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB4" t="inlineStr">
         <is>
           <t>0</t>
@@ -4194,12 +4209,12 @@
       </c>
       <c r="FF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
@@ -4219,170 +4234,175 @@
       </c>
       <c r="FK4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL4" t="inlineStr">
+      <c r="FM4" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM4" t="inlineStr">
+      <c r="FN4" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN4" t="inlineStr">
+      <c r="FO4" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO4" t="inlineStr">
+      <c r="FP4" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP4" t="inlineStr">
+      <c r="FQ4" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ4" t="inlineStr">
+      <c r="FR4" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR4" t="inlineStr">
+      <c r="FS4" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS4" t="inlineStr">
+      <c r="FT4" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT4" t="inlineStr">
+      <c r="FU4" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU4" t="inlineStr">
+      <c r="FV4" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV4" t="inlineStr">
+      <c r="FW4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW4" t="inlineStr">
+      <c r="FX4" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX4" t="inlineStr">
+      <c r="FY4" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY4" t="inlineStr">
+      <c r="FZ4" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ4" t="inlineStr">
+      <c r="GA4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA4" t="inlineStr">
+      <c r="GB4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB4" t="inlineStr">
+      <c r="GC4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE4" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG4" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG4" t="inlineStr">
+      <c r="GH4" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH4" t="inlineStr">
+      <c r="GI4" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI4" t="inlineStr">
+      <c r="GJ4" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ4" t="inlineStr">
+      <c r="GK4" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK4" t="inlineStr">
+      <c r="GL4" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL4" t="inlineStr">
+      <c r="GM4" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM4" t="inlineStr">
+      <c r="GN4" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN4" t="inlineStr">
+      <c r="GO4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO4" t="inlineStr">
+      <c r="GP4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP4" t="inlineStr">
+      <c r="GQ4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ4" t="inlineStr">
+      <c r="GR4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR4" t="inlineStr">
+      <c r="GS4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -4781,383 +4801,383 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>5.67</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>11.11</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>6.73</t>
         </is>
       </c>
-      <c r="CK5" t="n">
+      <c r="CL5" t="n">
         <v>-0.33</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CM5" t="n">
         <v>-1.41</v>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>-2.1</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>-2.26</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>211.7</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>212.95</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>214.72</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>219.34</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>224.42</t>
         </is>
       </c>
-      <c r="CT5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
           <t>-0.001415094339622724</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>-0.003043071161048738</t>
         </is>
       </c>
-      <c r="CW5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>-0.001279069767441854</t>
         </is>
       </c>
-      <c r="CX5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>-0.002365141453652408</t>
         </is>
       </c>
-      <c r="CY5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>-0.0007235688642752702</t>
         </is>
       </c>
-      <c r="CZ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
           <t>-6.95</t>
         </is>
       </c>
-      <c r="DB5" t="n">
+      <c r="DC5" t="n">
         <v>-2.34</v>
       </c>
-      <c r="DC5" t="n">
+      <c r="DD5" t="n">
         <v>-2.19</v>
       </c>
-      <c r="DD5" t="inlineStr">
+      <c r="DE5" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE5" t="inlineStr">
+      <c r="DF5" t="inlineStr">
         <is>
           <t>-153.39</t>
         </is>
       </c>
-      <c r="DF5" t="inlineStr">
+      <c r="DG5" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG5" t="inlineStr">
+      <c r="DH5" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH5" t="inlineStr">
+      <c r="DI5" t="inlineStr">
         <is>
           <t>242656285.0</t>
         </is>
       </c>
-      <c r="DI5" t="n">
+      <c r="DJ5" t="n">
         <v>401567743.4</v>
       </c>
-      <c r="DJ5" t="inlineStr">
+      <c r="DK5" t="inlineStr">
         <is>
           <t>402197533.1</t>
         </is>
       </c>
-      <c r="DK5" t="inlineStr">
+      <c r="DL5" t="inlineStr">
         <is>
           <t>360892111.8</t>
         </is>
       </c>
-      <c r="DL5" t="n">
+      <c r="DM5" t="n">
         <v>499527332.66</v>
       </c>
-      <c r="DM5" t="inlineStr">
+      <c r="DN5" t="inlineStr">
         <is>
           <t>636367710.4625</t>
         </is>
       </c>
-      <c r="DN5" t="inlineStr">
+      <c r="DO5" t="inlineStr">
         <is>
           <t>-2799714.510887335</t>
         </is>
       </c>
-      <c r="DO5" t="inlineStr">
+      <c r="DP5" t="inlineStr">
         <is>
           <t>11251584.09653378</t>
         </is>
       </c>
-      <c r="DP5" t="inlineStr">
+      <c r="DQ5" t="inlineStr">
         <is>
           <t>242656285.0</t>
         </is>
       </c>
-      <c r="DQ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS5" t="inlineStr">
+      <c r="DT5" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT5" t="inlineStr">
+      <c r="DU5" t="inlineStr">
         <is>
           <t>-6.64</t>
         </is>
       </c>
-      <c r="DU5" t="inlineStr">
+      <c r="DV5" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV5" t="inlineStr">
+      <c r="DW5" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW5" t="inlineStr">
+      <c r="DX5" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX5" t="inlineStr">
+      <c r="DY5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY5" t="inlineStr">
+      <c r="DZ5" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ5" t="inlineStr">
+      <c r="EA5" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA5" t="inlineStr">
+      <c r="EB5" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB5" t="inlineStr">
+      <c r="EC5" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC5" t="inlineStr">
+      <c r="ED5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED5" t="inlineStr">
+      <c r="EE5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE5" t="inlineStr">
+      <c r="EF5" t="inlineStr">
         <is>
           <t>5.35</t>
         </is>
       </c>
-      <c r="EF5" t="inlineStr">
+      <c r="EG5" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG5" t="inlineStr">
+      <c r="EH5" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI5" t="inlineStr">
+      <c r="EJ5" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ5" t="inlineStr">
+      <c r="EK5" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK5" t="inlineStr">
+      <c r="EL5" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL5" t="inlineStr">
+      <c r="EM5" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM5" t="inlineStr">
+      <c r="EN5" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN5" t="inlineStr">
+      <c r="EO5" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO5" t="inlineStr">
+      <c r="EP5" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP5" t="inlineStr">
+      <c r="EQ5" t="inlineStr">
         <is>
           <t>211.5</t>
         </is>
       </c>
-      <c r="EQ5" t="inlineStr">
+      <c r="ER5" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ER5" t="inlineStr">
+      <c r="ES5" t="inlineStr">
         <is>
           <t>210.0</t>
         </is>
       </c>
-      <c r="ES5" t="inlineStr">
+      <c r="ET5" t="inlineStr">
         <is>
           <t>211.0</t>
         </is>
       </c>
-      <c r="ET5" t="inlineStr">
+      <c r="EU5" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU5" t="inlineStr">
+      <c r="EV5" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV5" t="inlineStr">
+      <c r="EW5" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX5" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="FA5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB5" t="inlineStr">
         <is>
           <t>0</t>
@@ -5180,12 +5200,12 @@
       </c>
       <c r="FF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH5" t="inlineStr">
@@ -5205,170 +5225,175 @@
       </c>
       <c r="FK5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL5" t="inlineStr">
+      <c r="FM5" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM5" t="inlineStr">
+      <c r="FN5" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN5" t="inlineStr">
+      <c r="FO5" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO5" t="inlineStr">
+      <c r="FP5" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP5" t="inlineStr">
+      <c r="FQ5" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ5" t="inlineStr">
+      <c r="FR5" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR5" t="inlineStr">
+      <c r="FS5" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS5" t="inlineStr">
+      <c r="FT5" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT5" t="inlineStr">
+      <c r="FU5" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU5" t="inlineStr">
+      <c r="FV5" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV5" t="inlineStr">
+      <c r="FW5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW5" t="inlineStr">
+      <c r="FX5" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX5" t="inlineStr">
+      <c r="FY5" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY5" t="inlineStr">
+      <c r="FZ5" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ5" t="inlineStr">
+      <c r="GA5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA5" t="inlineStr">
+      <c r="GB5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB5" t="inlineStr">
+      <c r="GC5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE5" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG5" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG5" t="inlineStr">
+      <c r="GH5" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH5" t="inlineStr">
+      <c r="GI5" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI5" t="inlineStr">
+      <c r="GJ5" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ5" t="inlineStr">
+      <c r="GK5" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK5" t="inlineStr">
+      <c r="GL5" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL5" t="inlineStr">
+      <c r="GM5" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM5" t="inlineStr">
+      <c r="GN5" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN5" t="inlineStr">
+      <c r="GO5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO5" t="inlineStr">
+      <c r="GP5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP5" t="inlineStr">
+      <c r="GQ5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ5" t="inlineStr">
+      <c r="GR5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR5" t="inlineStr">
+      <c r="GS5" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -5767,383 +5792,383 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>14.71</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>-0.71</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CJ6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
           <t>6.06</t>
         </is>
       </c>
-      <c r="CK6" t="n">
+      <c r="CL6" t="n">
         <v>-0.71</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CM6" t="n">
         <v>-1.4</v>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>-2.21</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>-2.10</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>213.6</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>215.0</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>219.86</t>
         </is>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>224.58</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
           <t>-0.002352941176470558</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>-0.002102312543798224</t>
         </is>
       </c>
-      <c r="CW6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>-0.001509346336932449</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>-0.002631101433496541</t>
         </is>
       </c>
-      <c r="CY6" t="inlineStr">
+      <c r="CZ6" t="inlineStr">
         <is>
           <t>-0.0006396707086437914</t>
         </is>
       </c>
-      <c r="CZ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
           <t>-7.43</t>
         </is>
       </c>
-      <c r="DB6" t="n">
+      <c r="DC6" t="n">
         <v>-2.31</v>
       </c>
-      <c r="DC6" t="n">
+      <c r="DD6" t="n">
         <v>-2.15</v>
       </c>
-      <c r="DD6" t="inlineStr">
+      <c r="DE6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE6" t="inlineStr">
+      <c r="DF6" t="inlineStr">
         <is>
           <t>-152.47</t>
         </is>
       </c>
-      <c r="DF6" t="inlineStr">
+      <c r="DG6" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG6" t="inlineStr">
+      <c r="DH6" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH6" t="inlineStr">
+      <c r="DI6" t="inlineStr">
         <is>
           <t>627997406.0</t>
         </is>
       </c>
-      <c r="DI6" t="n">
+      <c r="DJ6" t="n">
         <v>446456989.4</v>
       </c>
-      <c r="DJ6" t="inlineStr">
+      <c r="DK6" t="inlineStr">
         <is>
           <t>402462830.4</t>
         </is>
       </c>
-      <c r="DK6" t="inlineStr">
+      <c r="DL6" t="inlineStr">
         <is>
           <t>367213800.2333333</t>
         </is>
       </c>
-      <c r="DL6" t="n">
+      <c r="DM6" t="n">
         <v>514612178.2</v>
       </c>
-      <c r="DM6" t="inlineStr">
+      <c r="DN6" t="inlineStr">
         <is>
           <t>644200383.275</t>
         </is>
       </c>
-      <c r="DN6" t="inlineStr">
+      <c r="DO6" t="inlineStr">
         <is>
           <t>-5354496.075872992</t>
         </is>
       </c>
-      <c r="DO6" t="inlineStr">
+      <c r="DP6" t="inlineStr">
         <is>
           <t>28645776.31716985</t>
         </is>
       </c>
-      <c r="DP6" t="inlineStr">
+      <c r="DQ6" t="inlineStr">
         <is>
           <t>627997406.0</t>
         </is>
       </c>
-      <c r="DQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS6" t="inlineStr">
+      <c r="DT6" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT6" t="inlineStr">
+      <c r="DU6" t="inlineStr">
         <is>
           <t>-6.86</t>
         </is>
       </c>
-      <c r="DU6" t="inlineStr">
+      <c r="DV6" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV6" t="inlineStr">
+      <c r="DW6" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW6" t="inlineStr">
+      <c r="DX6" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX6" t="inlineStr">
+      <c r="DY6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY6" t="inlineStr">
+      <c r="DZ6" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ6" t="inlineStr">
+      <c r="EA6" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA6" t="inlineStr">
+      <c r="EB6" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB6" t="inlineStr">
+      <c r="EC6" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC6" t="inlineStr">
+      <c r="ED6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
+      <c r="EE6" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE6" t="inlineStr">
+      <c r="EF6" t="inlineStr">
         <is>
           <t>5.34</t>
         </is>
       </c>
-      <c r="EF6" t="inlineStr">
+      <c r="EG6" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG6" t="inlineStr">
+      <c r="EH6" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH6" t="inlineStr">
+      <c r="EI6" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI6" t="inlineStr">
+      <c r="EJ6" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ6" t="inlineStr">
+      <c r="EK6" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK6" t="inlineStr">
+      <c r="EL6" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL6" t="inlineStr">
+      <c r="EM6" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM6" t="inlineStr">
+      <c r="EN6" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN6" t="inlineStr">
+      <c r="EO6" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO6" t="inlineStr">
+      <c r="EP6" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP6" t="inlineStr">
+      <c r="EQ6" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="EQ6" t="inlineStr">
+      <c r="ER6" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="ER6" t="inlineStr">
+      <c r="ES6" t="inlineStr">
         <is>
           <t>210.0</t>
         </is>
       </c>
-      <c r="ES6" t="inlineStr">
+      <c r="ET6" t="inlineStr">
         <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ET6" t="inlineStr">
+      <c r="EU6" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU6" t="inlineStr">
+      <c r="EV6" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV6" t="inlineStr">
+      <c r="EW6" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="FA6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB6" t="inlineStr">
         <is>
           <t>0</t>
@@ -6166,12 +6191,12 @@
       </c>
       <c r="FF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH6" t="inlineStr">
@@ -6191,170 +6216,175 @@
       </c>
       <c r="FK6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL6" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL6" t="inlineStr">
+      <c r="FM6" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM6" t="inlineStr">
+      <c r="FN6" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN6" t="inlineStr">
+      <c r="FO6" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO6" t="inlineStr">
+      <c r="FP6" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP6" t="inlineStr">
+      <c r="FQ6" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ6" t="inlineStr">
+      <c r="FR6" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR6" t="inlineStr">
+      <c r="FS6" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS6" t="inlineStr">
+      <c r="FT6" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT6" t="inlineStr">
+      <c r="FU6" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU6" t="inlineStr">
+      <c r="FV6" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV6" t="inlineStr">
+      <c r="FW6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW6" t="inlineStr">
+      <c r="FX6" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX6" t="inlineStr">
+      <c r="FY6" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY6" t="inlineStr">
+      <c r="FZ6" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ6" t="inlineStr">
+      <c r="GA6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA6" t="inlineStr">
+      <c r="GB6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB6" t="inlineStr">
+      <c r="GC6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE6" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG6" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG6" t="inlineStr">
+      <c r="GH6" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH6" t="inlineStr">
+      <c r="GI6" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI6" t="inlineStr">
+      <c r="GJ6" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ6" t="inlineStr">
+      <c r="GK6" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK6" t="inlineStr">
+      <c r="GL6" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL6" t="inlineStr">
+      <c r="GM6" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM6" t="inlineStr">
+      <c r="GN6" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN6" t="inlineStr">
+      <c r="GO6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO6" t="inlineStr">
+      <c r="GP6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP6" t="inlineStr">
+      <c r="GQ6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ6" t="inlineStr">
+      <c r="GR6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR6" t="inlineStr">
+      <c r="GS6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -6753,383 +6783,383 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>10.89</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>9.09</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>6.06</t>
         </is>
       </c>
-      <c r="CK7" t="n">
+      <c r="CL7" t="n">
         <v>0</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CM7" t="n">
         <v>-1.31</v>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>-2.32</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>-1.91</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>214.05</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>215.32</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>220.44</t>
         </is>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>224.72</t>
         </is>
       </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
           <t>-0.00140977443609025</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>-0.001399580125962085</t>
         </is>
       </c>
-      <c r="CW7" t="inlineStr">
+      <c r="CX7" t="inlineStr">
         <is>
           <t>-0.0008120649651972567</t>
         </is>
       </c>
-      <c r="CX7" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>-0.00275955666138894</t>
         </is>
       </c>
-      <c r="CY7" t="inlineStr">
+      <c r="CZ7" t="inlineStr">
         <is>
           <t>-0.001083483817196806</t>
         </is>
       </c>
-      <c r="CZ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
           <t>-3.62</t>
         </is>
       </c>
-      <c r="DB7" t="n">
+      <c r="DC7" t="n">
         <v>-2.19</v>
       </c>
-      <c r="DC7" t="n">
+      <c r="DD7" t="n">
         <v>-2.11</v>
       </c>
-      <c r="DD7" t="inlineStr">
+      <c r="DE7" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE7" t="inlineStr">
+      <c r="DF7" t="inlineStr">
         <is>
           <t>-151.49</t>
         </is>
       </c>
-      <c r="DF7" t="inlineStr">
+      <c r="DG7" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG7" t="inlineStr">
+      <c r="DH7" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH7" t="inlineStr">
+      <c r="DI7" t="inlineStr">
         <is>
           <t>467278976.0</t>
         </is>
       </c>
-      <c r="DI7" t="n">
+      <c r="DJ7" t="n">
         <v>418130651</v>
       </c>
-      <c r="DJ7" t="inlineStr">
+      <c r="DK7" t="inlineStr">
         <is>
           <t>371868657.7</t>
         </is>
       </c>
-      <c r="DK7" t="inlineStr">
+      <c r="DL7" t="inlineStr">
         <is>
           <t>365219125.0</t>
         </is>
       </c>
-      <c r="DL7" t="n">
+      <c r="DM7" t="n">
         <v>527411299.66</v>
       </c>
-      <c r="DM7" t="inlineStr">
+      <c r="DN7" t="inlineStr">
         <is>
           <t>653166606.5875</t>
         </is>
       </c>
-      <c r="DN7" t="inlineStr">
+      <c r="DO7" t="inlineStr">
         <is>
           <t>-11536363.78369896</t>
         </is>
       </c>
-      <c r="DO7" t="inlineStr">
+      <c r="DP7" t="inlineStr">
         <is>
           <t>11185010.22817957</t>
         </is>
       </c>
-      <c r="DP7" t="inlineStr">
+      <c r="DQ7" t="inlineStr">
         <is>
           <t>467278976.0</t>
         </is>
       </c>
-      <c r="DQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS7" t="inlineStr">
+      <c r="DT7" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT7" t="inlineStr">
+      <c r="DU7" t="inlineStr">
         <is>
           <t>-5.97</t>
         </is>
       </c>
-      <c r="DU7" t="inlineStr">
+      <c r="DV7" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV7" t="inlineStr">
+      <c r="DW7" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW7" t="inlineStr">
+      <c r="DX7" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX7" t="inlineStr">
+      <c r="DY7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY7" t="inlineStr">
+      <c r="DZ7" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ7" t="inlineStr">
+      <c r="EA7" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA7" t="inlineStr">
+      <c r="EB7" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB7" t="inlineStr">
+      <c r="EC7" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
+      <c r="ED7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
+      <c r="EE7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE7" t="inlineStr">
+      <c r="EF7" t="inlineStr">
         <is>
           <t>5.39</t>
         </is>
       </c>
-      <c r="EF7" t="inlineStr">
+      <c r="EG7" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG7" t="inlineStr">
+      <c r="EH7" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH7" t="inlineStr">
+      <c r="EI7" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI7" t="inlineStr">
+      <c r="EJ7" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ7" t="inlineStr">
+      <c r="EK7" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK7" t="inlineStr">
+      <c r="EL7" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL7" t="inlineStr">
+      <c r="EM7" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM7" t="inlineStr">
+      <c r="EN7" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN7" t="inlineStr">
+      <c r="EO7" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO7" t="inlineStr">
+      <c r="EP7" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP7" t="inlineStr">
+      <c r="EQ7" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="EQ7" t="inlineStr">
+      <c r="ER7" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="ER7" t="inlineStr">
+      <c r="ES7" t="inlineStr">
         <is>
           <t>210.5</t>
         </is>
       </c>
-      <c r="ES7" t="inlineStr">
+      <c r="ET7" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="ET7" t="inlineStr">
+      <c r="EU7" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU7" t="inlineStr">
+      <c r="EV7" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV7" t="inlineStr">
+      <c r="EW7" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX7" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="EY7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="FA7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB7" t="inlineStr">
         <is>
           <t>0</t>
@@ -7152,12 +7182,12 @@
       </c>
       <c r="FF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH7" t="inlineStr">
@@ -7177,170 +7207,175 @@
       </c>
       <c r="FK7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL7" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL7" t="inlineStr">
+      <c r="FM7" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM7" t="inlineStr">
+      <c r="FN7" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN7" t="inlineStr">
+      <c r="FO7" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO7" t="inlineStr">
+      <c r="FP7" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP7" t="inlineStr">
+      <c r="FQ7" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ7" t="inlineStr">
+      <c r="FR7" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR7" t="inlineStr">
+      <c r="FS7" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS7" t="inlineStr">
+      <c r="FT7" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT7" t="inlineStr">
+      <c r="FU7" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU7" t="inlineStr">
+      <c r="FV7" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV7" t="inlineStr">
+      <c r="FW7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW7" t="inlineStr">
+      <c r="FX7" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX7" t="inlineStr">
+      <c r="FY7" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY7" t="inlineStr">
+      <c r="FZ7" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ7" t="inlineStr">
+      <c r="GA7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA7" t="inlineStr">
+      <c r="GB7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB7" t="inlineStr">
+      <c r="GC7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE7" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG7" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG7" t="inlineStr">
+      <c r="GH7" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH7" t="inlineStr">
+      <c r="GI7" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI7" t="inlineStr">
+      <c r="GJ7" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ7" t="inlineStr">
+      <c r="GK7" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK7" t="inlineStr">
+      <c r="GL7" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL7" t="inlineStr">
+      <c r="GM7" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM7" t="inlineStr">
+      <c r="GN7" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN7" t="inlineStr">
+      <c r="GO7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO7" t="inlineStr">
+      <c r="GP7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP7" t="inlineStr">
+      <c r="GQ7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ7" t="inlineStr">
+      <c r="GR7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR7" t="inlineStr">
+      <c r="GS7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -7739,383 +7774,383 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>8.19</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>-0.47</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>9.09</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>3.03</t>
         </is>
       </c>
-      <c r="CK8" t="n">
+      <c r="CL8" t="n">
         <v>-0.14</v>
       </c>
-      <c r="CL8" t="n">
+      <c r="CM8" t="n">
         <v>-1.25</v>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>-2.51</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>-1.74</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>212.8</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>214.35</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>215.5</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>221.05</t>
         </is>
       </c>
-      <c r="CS8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>224.97</t>
         </is>
       </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
           <t>-0.002344116268166885</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>-0.001862630966239842</t>
         </is>
       </c>
-      <c r="CW8" t="inlineStr">
+      <c r="CX8" t="inlineStr">
         <is>
           <t>-0.0009272137227630539</t>
         </is>
       </c>
-      <c r="CX8" t="inlineStr">
+      <c r="CY8" t="inlineStr">
         <is>
           <t>-0.002796950421798061</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
+      <c r="CZ8" t="inlineStr">
         <is>
           <t>-0.00185791137485436</t>
         </is>
       </c>
-      <c r="CZ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
           <t>-5.27</t>
         </is>
       </c>
-      <c r="DB8" t="n">
+      <c r="DC8" t="n">
         <v>-2.2</v>
       </c>
-      <c r="DC8" t="n">
+      <c r="DD8" t="n">
         <v>-2.09</v>
       </c>
-      <c r="DD8" t="inlineStr">
+      <c r="DE8" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE8" t="inlineStr">
+      <c r="DF8" t="inlineStr">
         <is>
           <t>-151.02</t>
         </is>
       </c>
-      <c r="DF8" t="inlineStr">
+      <c r="DG8" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG8" t="inlineStr">
+      <c r="DH8" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH8" t="inlineStr">
+      <c r="DI8" t="inlineStr">
         <is>
           <t>353129823.0</t>
         </is>
       </c>
-      <c r="DI8" t="n">
+      <c r="DJ8" t="n">
         <v>366032679.6</v>
       </c>
-      <c r="DJ8" t="inlineStr">
+      <c r="DK8" t="inlineStr">
         <is>
           <t>349409181.6</t>
         </is>
       </c>
-      <c r="DK8" t="inlineStr">
+      <c r="DL8" t="inlineStr">
         <is>
           <t>361747717.0333334</t>
         </is>
       </c>
-      <c r="DL8" t="n">
+      <c r="DM8" t="n">
         <v>541988911.52</v>
       </c>
-      <c r="DM8" t="inlineStr">
+      <c r="DN8" t="inlineStr">
         <is>
           <t>663738938.0125</t>
         </is>
       </c>
-      <c r="DN8" t="inlineStr">
+      <c r="DO8" t="inlineStr">
         <is>
           <t>-15667522.6949496</t>
         </is>
       </c>
-      <c r="DO8" t="inlineStr">
+      <c r="DP8" t="inlineStr">
         <is>
           <t>3061425.80718708</t>
         </is>
       </c>
-      <c r="DP8" t="inlineStr">
+      <c r="DQ8" t="inlineStr">
         <is>
           <t>353129823.0</t>
         </is>
       </c>
-      <c r="DQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS8" t="inlineStr">
+      <c r="DT8" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT8" t="inlineStr">
+      <c r="DU8" t="inlineStr">
         <is>
           <t>-5.97</t>
         </is>
       </c>
-      <c r="DU8" t="inlineStr">
+      <c r="DV8" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV8" t="inlineStr">
+      <c r="DW8" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW8" t="inlineStr">
+      <c r="DX8" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX8" t="inlineStr">
+      <c r="DY8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY8" t="inlineStr">
+      <c r="DZ8" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ8" t="inlineStr">
+      <c r="EA8" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA8" t="inlineStr">
+      <c r="EB8" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB8" t="inlineStr">
+      <c r="EC8" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC8" t="inlineStr">
+      <c r="ED8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
+      <c r="EE8" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="EE8" t="inlineStr">
+      <c r="EF8" t="inlineStr">
         <is>
           <t>5.39</t>
         </is>
       </c>
-      <c r="EF8" t="inlineStr">
+      <c r="EG8" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG8" t="inlineStr">
+      <c r="EH8" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH8" t="inlineStr">
+      <c r="EI8" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI8" t="inlineStr">
+      <c r="EJ8" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ8" t="inlineStr">
+      <c r="EK8" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK8" t="inlineStr">
+      <c r="EL8" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL8" t="inlineStr">
+      <c r="EM8" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM8" t="inlineStr">
+      <c r="EN8" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN8" t="inlineStr">
+      <c r="EO8" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO8" t="inlineStr">
+      <c r="EP8" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP8" t="inlineStr">
+      <c r="EQ8" t="inlineStr">
         <is>
           <t>214.0</t>
         </is>
       </c>
-      <c r="EQ8" t="inlineStr">
+      <c r="ER8" t="inlineStr">
         <is>
           <t>214.0</t>
         </is>
       </c>
-      <c r="ER8" t="inlineStr">
+      <c r="ES8" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ES8" t="inlineStr">
+      <c r="ET8" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="ET8" t="inlineStr">
+      <c r="EU8" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU8" t="inlineStr">
+      <c r="EV8" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV8" t="inlineStr">
+      <c r="EW8" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX8" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="EY8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="FA8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB8" t="inlineStr">
         <is>
           <t>0</t>
@@ -8138,12 +8173,12 @@
       </c>
       <c r="FF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH8" t="inlineStr">
@@ -8163,170 +8198,175 @@
       </c>
       <c r="FK8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL8" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL8" t="inlineStr">
+      <c r="FM8" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM8" t="inlineStr">
+      <c r="FN8" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN8" t="inlineStr">
+      <c r="FO8" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO8" t="inlineStr">
+      <c r="FP8" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP8" t="inlineStr">
+      <c r="FQ8" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ8" t="inlineStr">
+      <c r="FR8" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR8" t="inlineStr">
+      <c r="FS8" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS8" t="inlineStr">
+      <c r="FT8" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT8" t="inlineStr">
+      <c r="FU8" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU8" t="inlineStr">
+      <c r="FV8" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV8" t="inlineStr">
+      <c r="FW8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW8" t="inlineStr">
+      <c r="FX8" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX8" t="inlineStr">
+      <c r="FY8" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY8" t="inlineStr">
+      <c r="FZ8" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ8" t="inlineStr">
+      <c r="GA8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA8" t="inlineStr">
+      <c r="GB8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB8" t="inlineStr">
+      <c r="GC8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE8" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG8" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG8" t="inlineStr">
+      <c r="GH8" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH8" t="inlineStr">
+      <c r="GI8" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI8" t="inlineStr">
+      <c r="GJ8" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ8" t="inlineStr">
+      <c r="GK8" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK8" t="inlineStr">
+      <c r="GL8" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL8" t="inlineStr">
+      <c r="GM8" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM8" t="inlineStr">
+      <c r="GN8" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN8" t="inlineStr">
+      <c r="GO8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO8" t="inlineStr">
+      <c r="GP8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP8" t="inlineStr">
+      <c r="GQ8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ8" t="inlineStr">
+      <c r="GR8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR8" t="inlineStr">
+      <c r="GS8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -8725,383 +8765,383 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>7.36</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr"/>
-      <c r="CG9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CJ9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CK9" t="n">
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CL9" t="n">
         <v>-0.61</v>
       </c>
-      <c r="CL9" t="n">
+      <c r="CM9" t="n">
         <v>-1.11</v>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>-2.69</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>-1.65</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>213.3</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>214.75</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>215.7</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>221.67</t>
         </is>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>225.39</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
           <t>-0.004201680672268782</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>-0.002091078066914442</t>
         </is>
       </c>
-      <c r="CW9" t="inlineStr">
+      <c r="CX9" t="inlineStr">
         <is>
           <t>-0.0015044555028354</t>
         </is>
       </c>
-      <c r="CX9" t="inlineStr">
+      <c r="CY9" t="inlineStr">
         <is>
           <t>-0.002789149309460615</t>
         </is>
       </c>
-      <c r="CY9" t="inlineStr">
+      <c r="CZ9" t="inlineStr">
         <is>
           <t>-0.001495182190718869</t>
         </is>
       </c>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
           <t>-6.02</t>
         </is>
       </c>
-      <c r="DB9" t="n">
+      <c r="DC9" t="n">
         <v>-2.19</v>
       </c>
-      <c r="DC9" t="n">
+      <c r="DD9" t="n">
         <v>-2.06</v>
       </c>
-      <c r="DD9" t="inlineStr">
+      <c r="DE9" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE9" t="inlineStr">
+      <c r="DF9" t="inlineStr">
         <is>
           <t>-150.35</t>
         </is>
       </c>
-      <c r="DF9" t="inlineStr">
+      <c r="DG9" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG9" t="inlineStr">
+      <c r="DH9" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH9" t="inlineStr">
+      <c r="DI9" t="inlineStr">
         <is>
           <t>316776227.0</t>
         </is>
       </c>
-      <c r="DI9" t="n">
+      <c r="DJ9" t="n">
         <v>345663307.4</v>
       </c>
-      <c r="DJ9" t="inlineStr">
+      <c r="DK9" t="inlineStr">
         <is>
           <t>336188816.6</t>
         </is>
       </c>
-      <c r="DK9" t="inlineStr">
+      <c r="DL9" t="inlineStr">
         <is>
           <t>367617217.2</t>
         </is>
       </c>
-      <c r="DL9" t="n">
+      <c r="DM9" t="n">
         <v>561834701.02</v>
       </c>
-      <c r="DM9" t="inlineStr">
+      <c r="DN9" t="inlineStr">
         <is>
           <t>700692145.4125</t>
         </is>
       </c>
-      <c r="DN9" t="inlineStr">
+      <c r="DO9" t="inlineStr">
         <is>
           <t>-19072786.05897446</t>
         </is>
       </c>
-      <c r="DO9" t="inlineStr">
+      <c r="DP9" t="inlineStr">
         <is>
           <t>3577234.962655425</t>
         </is>
       </c>
-      <c r="DP9" t="inlineStr">
+      <c r="DQ9" t="inlineStr">
         <is>
           <t>316776227.0</t>
         </is>
       </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS9" t="inlineStr">
+      <c r="DT9" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT9" t="inlineStr">
+      <c r="DU9" t="inlineStr">
         <is>
           <t>-6.19</t>
         </is>
       </c>
-      <c r="DU9" t="inlineStr">
+      <c r="DV9" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV9" t="inlineStr">
+      <c r="DW9" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW9" t="inlineStr">
+      <c r="DX9" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX9" t="inlineStr">
+      <c r="DY9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY9" t="inlineStr">
+      <c r="DZ9" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ9" t="inlineStr">
+      <c r="EA9" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA9" t="inlineStr">
+      <c r="EB9" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB9" t="inlineStr">
+      <c r="EC9" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC9" t="inlineStr">
+      <c r="ED9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
+      <c r="EE9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE9" t="inlineStr">
+      <c r="EF9" t="inlineStr">
         <is>
           <t>5.38</t>
         </is>
       </c>
-      <c r="EF9" t="inlineStr">
+      <c r="EG9" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG9" t="inlineStr">
+      <c r="EH9" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH9" t="inlineStr">
+      <c r="EI9" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI9" t="inlineStr">
+      <c r="EJ9" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ9" t="inlineStr">
+      <c r="EK9" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK9" t="inlineStr">
+      <c r="EL9" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL9" t="inlineStr">
+      <c r="EM9" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM9" t="inlineStr">
+      <c r="EN9" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN9" t="inlineStr">
+      <c r="EO9" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO9" t="inlineStr">
+      <c r="EP9" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP9" t="inlineStr">
+      <c r="EQ9" t="inlineStr">
         <is>
           <t>213.0</t>
         </is>
       </c>
-      <c r="EQ9" t="inlineStr">
+      <c r="ER9" t="inlineStr">
         <is>
           <t>213.0</t>
         </is>
       </c>
-      <c r="ER9" t="inlineStr">
+      <c r="ES9" t="inlineStr">
         <is>
           <t>211.5</t>
         </is>
       </c>
-      <c r="ES9" t="inlineStr">
+      <c r="ET9" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ET9" t="inlineStr">
+      <c r="EU9" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU9" t="inlineStr">
+      <c r="EV9" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV9" t="inlineStr">
+      <c r="EW9" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX9" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EY9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="FA9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB9" t="inlineStr">
         <is>
           <t>0</t>
@@ -9124,12 +9164,12 @@
       </c>
       <c r="FF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH9" t="inlineStr">
@@ -9149,170 +9189,175 @@
       </c>
       <c r="FK9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL9" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL9" t="inlineStr">
+      <c r="FM9" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM9" t="inlineStr">
+      <c r="FN9" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN9" t="inlineStr">
+      <c r="FO9" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO9" t="inlineStr">
+      <c r="FP9" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP9" t="inlineStr">
+      <c r="FQ9" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ9" t="inlineStr">
+      <c r="FR9" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR9" t="inlineStr">
+      <c r="FS9" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS9" t="inlineStr">
+      <c r="FT9" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT9" t="inlineStr">
+      <c r="FU9" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU9" t="inlineStr">
+      <c r="FV9" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV9" t="inlineStr">
+      <c r="FW9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW9" t="inlineStr">
+      <c r="FX9" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX9" t="inlineStr">
+      <c r="FY9" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY9" t="inlineStr">
+      <c r="FZ9" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ9" t="inlineStr">
+      <c r="GA9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA9" t="inlineStr">
+      <c r="GB9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB9" t="inlineStr">
+      <c r="GC9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE9" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG9" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG9" t="inlineStr">
+      <c r="GH9" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH9" t="inlineStr">
+      <c r="GI9" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI9" t="inlineStr">
+      <c r="GJ9" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ9" t="inlineStr">
+      <c r="GK9" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK9" t="inlineStr">
+      <c r="GL9" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL9" t="inlineStr">
+      <c r="GM9" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM9" t="inlineStr">
+      <c r="GN9" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN9" t="inlineStr">
+      <c r="GO9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO9" t="inlineStr">
+      <c r="GP9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP9" t="inlineStr">
+      <c r="GQ9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ9" t="inlineStr">
+      <c r="GR9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR9" t="inlineStr">
+      <c r="GS9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
@@ -9711,383 +9756,383 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
           <t>2026-05-22 00:00:00</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>10.83</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>-0.23</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr"/>
-      <c r="CG10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>1914</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="CJ10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CK10" t="n">
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="CL10" t="n">
         <v>-0.79</v>
       </c>
-      <c r="CL10" t="n">
+      <c r="CM10" t="n">
         <v>-0.84</v>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>-2.82</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>-1.52</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>214.2</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>215.2</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>216.02</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>222.29</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>225.72</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
           <t>-0.004646840148698872</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>-0.002780352177942591</t>
         </is>
       </c>
-      <c r="CW10" t="inlineStr">
+      <c r="CX10" t="inlineStr">
         <is>
           <t>-0.001848215317084456</t>
         </is>
       </c>
-      <c r="CX10" t="inlineStr">
+      <c r="CY10" t="inlineStr">
         <is>
           <t>-0.002960305001121322</t>
         </is>
       </c>
-      <c r="CY10" t="inlineStr">
+      <c r="CZ10" t="inlineStr">
         <is>
           <t>-0.001133943634704204</t>
         </is>
       </c>
-      <c r="CZ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DA10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
           <t>-2.73</t>
         </is>
       </c>
-      <c r="DB10" t="n">
+      <c r="DC10" t="n">
         <v>-2.09</v>
       </c>
-      <c r="DC10" t="n">
+      <c r="DD10" t="n">
         <v>-2.03</v>
       </c>
-      <c r="DD10" t="inlineStr">
+      <c r="DE10" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="DE10" t="inlineStr">
+      <c r="DF10" t="inlineStr">
         <is>
           <t>-149.59</t>
         </is>
       </c>
-      <c r="DF10" t="inlineStr">
+      <c r="DG10" t="inlineStr">
         <is>
           <t>2026/10/07</t>
         </is>
       </c>
-      <c r="DG10" t="inlineStr">
+      <c r="DH10" t="inlineStr">
         <is>
           <t>1108834326.963768</t>
         </is>
       </c>
-      <c r="DH10" t="inlineStr">
+      <c r="DI10" t="inlineStr">
         <is>
           <t>467102515.0</t>
         </is>
       </c>
-      <c r="DI10" t="n">
+      <c r="DJ10" t="n">
         <v>402827322.8</v>
       </c>
-      <c r="DJ10" t="inlineStr">
+      <c r="DK10" t="inlineStr">
         <is>
           <t>328319392.3</t>
         </is>
       </c>
-      <c r="DK10" t="inlineStr">
+      <c r="DL10" t="inlineStr">
         <is>
           <t>376703314.4666666</t>
         </is>
       </c>
-      <c r="DL10" t="n">
+      <c r="DM10" t="n">
         <v>582922481.98</v>
       </c>
-      <c r="DM10" t="inlineStr">
+      <c r="DN10" t="inlineStr">
         <is>
           <t>734035263.775</t>
         </is>
       </c>
-      <c r="DN10" t="inlineStr">
+      <c r="DO10" t="inlineStr">
         <is>
           <t>-23190971.6992708</t>
         </is>
       </c>
-      <c r="DO10" t="inlineStr">
+      <c r="DP10" t="inlineStr">
         <is>
           <t>8081374.936086774</t>
         </is>
       </c>
-      <c r="DP10" t="inlineStr">
+      <c r="DQ10" t="inlineStr">
         <is>
           <t>467102515.0</t>
         </is>
       </c>
-      <c r="DQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="DR10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
           <t>226.0</t>
         </is>
       </c>
-      <c r="DS10" t="inlineStr">
+      <c r="DT10" t="inlineStr">
         <is>
           <t>2026/06/25</t>
         </is>
       </c>
-      <c r="DT10" t="inlineStr">
+      <c r="DU10" t="inlineStr">
         <is>
           <t>-5.97</t>
         </is>
       </c>
-      <c r="DU10" t="inlineStr">
+      <c r="DV10" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DV10" t="inlineStr">
+      <c r="DW10" t="inlineStr">
         <is>
           <t>統一超</t>
         </is>
       </c>
-      <c r="DW10" t="inlineStr">
+      <c r="DX10" t="inlineStr">
         <is>
           <t>貿易百貨</t>
         </is>
       </c>
-      <c r="DX10" t="inlineStr">
+      <c r="DY10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="DY10" t="inlineStr">
+      <c r="DZ10" t="inlineStr">
         <is>
           <t>-0.03</t>
         </is>
       </c>
-      <c r="DZ10" t="inlineStr">
+      <c r="EA10" t="inlineStr">
         <is>
           <t>0.5136495342743107</t>
         </is>
       </c>
-      <c r="EA10" t="inlineStr">
+      <c r="EB10" t="inlineStr">
         <is>
           <t>4.882515139066092</t>
         </is>
       </c>
-      <c r="EB10" t="inlineStr">
+      <c r="EC10" t="inlineStr">
         <is>
           <t>4.66483663592919</t>
         </is>
       </c>
-      <c r="EC10" t="inlineStr">
+      <c r="ED10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="ED10" t="inlineStr">
+      <c r="EE10" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="EE10" t="inlineStr">
+      <c r="EF10" t="inlineStr">
         <is>
           <t>5.39</t>
         </is>
       </c>
-      <c r="EF10" t="inlineStr">
+      <c r="EG10" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="EG10" t="inlineStr">
+      <c r="EH10" t="inlineStr">
         <is>
           <t>88.66</t>
         </is>
       </c>
-      <c r="EH10" t="inlineStr">
+      <c r="EI10" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="EI10" t="inlineStr">
+      <c r="EJ10" t="inlineStr">
         <is>
           <t>34.59%</t>
         </is>
       </c>
-      <c r="EJ10" t="inlineStr">
+      <c r="EK10" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="EK10" t="inlineStr">
+      <c r="EL10" t="inlineStr">
         <is>
           <t>77.83</t>
         </is>
       </c>
-      <c r="EL10" t="inlineStr">
+      <c r="EM10" t="inlineStr">
         <is>
           <t>221439</t>
         </is>
       </c>
-      <c r="EM10" t="inlineStr">
+      <c r="EN10" t="inlineStr">
         <is>
           <t>便利商店62.08%、流通業務29.67%、其他7.34%、物流0.90% (2025年)</t>
         </is>
       </c>
-      <c r="EN10" t="inlineStr">
+      <c r="EO10" t="inlineStr">
         <is>
           <t>統一超-貿易百貨-上市</t>
         </is>
       </c>
-      <c r="EO10" t="inlineStr">
+      <c r="EP10" t="inlineStr">
         <is>
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="EP10" t="inlineStr">
+      <c r="EQ10" t="inlineStr">
         <is>
           <t>213.0</t>
         </is>
       </c>
-      <c r="EQ10" t="inlineStr">
+      <c r="ER10" t="inlineStr">
         <is>
           <t>213.5</t>
         </is>
       </c>
-      <c r="ER10" t="inlineStr">
+      <c r="ES10" t="inlineStr">
         <is>
           <t>212.0</t>
         </is>
       </c>
-      <c r="ES10" t="inlineStr">
+      <c r="ET10" t="inlineStr">
         <is>
           <t>212.5</t>
         </is>
       </c>
-      <c r="ET10" t="inlineStr">
+      <c r="EU10" t="inlineStr">
         <is>
           <t>206.5</t>
         </is>
       </c>
-      <c r="EU10" t="inlineStr">
+      <c r="EV10" t="inlineStr">
         <is>
           <t>39.41</t>
         </is>
       </c>
-      <c r="EV10" t="inlineStr">
+      <c r="EW10" t="inlineStr">
         <is>
           <t>** 貿易百貨 - 零售通路</t>
         </is>
       </c>
-      <c r="EW10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="EX10" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="EY10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="EY10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="EZ10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FA10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="FA10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="FB10" t="inlineStr">
         <is>
           <t>0</t>
@@ -10110,12 +10155,12 @@
       </c>
       <c r="FF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="FG10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="FH10" t="inlineStr">
@@ -10135,170 +10180,175 @@
       </c>
       <c r="FK10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="FL10" t="inlineStr">
+        <is>
           <t>115.2Q</t>
         </is>
       </c>
-      <c r="FL10" t="inlineStr">
+      <c r="FM10" t="inlineStr">
         <is>
           <t>92176.0</t>
         </is>
       </c>
-      <c r="FM10" t="inlineStr">
+      <c r="FN10" t="inlineStr">
         <is>
           <t>60295.0</t>
         </is>
       </c>
-      <c r="FN10" t="inlineStr">
+      <c r="FO10" t="inlineStr">
         <is>
           <t>31881.0</t>
         </is>
       </c>
-      <c r="FO10" t="inlineStr">
+      <c r="FP10" t="inlineStr">
         <is>
           <t>34.59</t>
         </is>
       </c>
-      <c r="FP10" t="inlineStr">
+      <c r="FQ10" t="inlineStr">
         <is>
           <t>3845.0</t>
         </is>
       </c>
-      <c r="FQ10" t="inlineStr">
+      <c r="FR10" t="inlineStr">
         <is>
           <t>4.17%</t>
         </is>
       </c>
-      <c r="FR10" t="inlineStr">
+      <c r="FS10" t="inlineStr">
         <is>
           <t>862.0</t>
         </is>
       </c>
-      <c r="FS10" t="inlineStr">
+      <c r="FT10" t="inlineStr">
         <is>
           <t>4708.0</t>
         </is>
       </c>
-      <c r="FT10" t="inlineStr">
+      <c r="FU10" t="inlineStr">
         <is>
           <t>3174.0</t>
         </is>
       </c>
-      <c r="FU10" t="inlineStr">
+      <c r="FV10" t="inlineStr">
         <is>
           <t>3.05</t>
         </is>
       </c>
-      <c r="FV10" t="inlineStr">
+      <c r="FW10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="FW10" t="inlineStr">
+      <c r="FX10" t="inlineStr">
         <is>
           <t>EPS成長 / 毛利率成長</t>
         </is>
       </c>
-      <c r="FX10" t="inlineStr">
+      <c r="FY10" t="inlineStr">
         <is>
           <t>2.73125</t>
         </is>
       </c>
-      <c r="FY10" t="inlineStr">
+      <c r="FZ10" t="inlineStr">
         <is>
           <t>34.385</t>
         </is>
       </c>
-      <c r="FZ10" t="inlineStr">
+      <c r="GA10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GA10" t="inlineStr">
+      <c r="GB10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GB10" t="inlineStr">
+      <c r="GC10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GC10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GD10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GE10" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GE10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="GF10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="GG10" t="inlineStr">
+        <is>
           <t>0.07999999999999963</t>
         </is>
       </c>
-      <c r="GG10" t="inlineStr">
+      <c r="GH10" t="inlineStr">
         <is>
           <t>0.02693602693602681</t>
         </is>
       </c>
-      <c r="GH10" t="inlineStr">
+      <c r="GI10" t="inlineStr">
         <is>
           <t>0.01000000000000512</t>
         </is>
       </c>
-      <c r="GI10" t="inlineStr">
+      <c r="GJ10" t="inlineStr">
         <is>
           <t>0.0002891844997110482</t>
         </is>
       </c>
-      <c r="GJ10" t="inlineStr">
+      <c r="GK10" t="inlineStr">
         <is>
           <t>0.1199999999999997</t>
         </is>
       </c>
-      <c r="GK10" t="inlineStr">
+      <c r="GL10" t="inlineStr">
         <is>
           <t>0.04095563139931735</t>
         </is>
       </c>
-      <c r="GL10" t="inlineStr">
+      <c r="GM10" t="inlineStr">
         <is>
           <t>0.1600000000000037</t>
         </is>
       </c>
-      <c r="GM10" t="inlineStr">
+      <c r="GN10" t="inlineStr">
         <is>
           <t>0.004647110078420003</t>
         </is>
       </c>
-      <c r="GN10" t="inlineStr">
+      <c r="GO10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GO10" t="inlineStr">
+      <c r="GP10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GP10" t="inlineStr">
+      <c r="GQ10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GQ10" t="inlineStr">
+      <c r="GR10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="GR10" t="inlineStr">
+      <c r="GS10" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
